--- a/教师伦理学2026.xlsx
+++ b/教师伦理学2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B657"/>
+  <dimension ref="A1:B650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5486,23 +5486,6 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>00299_单选题
-应用伦理学是研究如何应用伦理原则和道德规范来解决实际问题的学科，是对（     ）进行道德审视的科学。（该题目已移除！）
-A.伦理学的本质和基础；
-B.道德行为；
-C.社会生活的各个领域；
-D.伦理学；</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
           <t>00300_单选题
 教师在面对学生的学术不端行为时应如何处理？（     ）
 A.严格遵循学术规范进行处理；
@@ -5511,14 +5494,14 @@
 D.忽略问题；</t>
         </is>
       </c>
-      <c r="B300" t="inlineStr">
+      <c r="B299" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
+    <row r="300">
+      <c r="A300" t="inlineStr">
         <is>
           <t>00301_单选题
 规范伦理学中的道德规范是指（     ）。
@@ -5528,14 +5511,14 @@
 D.研究伦理的规范和价值观念；</t>
         </is>
       </c>
-      <c r="B301" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
+    <row r="301">
+      <c r="A301" t="inlineStr">
         <is>
           <t>00302_单选题
 教师伦理约束功能中的社会监督不包括（     ）。
@@ -5545,14 +5528,14 @@
 D.政府部门的定期检查；</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr">
+      <c r="B301" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
+    <row r="302">
+      <c r="A302" t="inlineStr">
         <is>
           <t>00303_单选题
 评价功能基于（     ），对教师的多维度进行全面评估。
@@ -5562,14 +5545,14 @@
 D.法律规范和制度要求；</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
+    <row r="303">
+      <c r="A303" t="inlineStr">
         <is>
           <t>00304_单选题
 高校教师在社会服务中应遵循的伦理准则是什么？（     ）
@@ -5579,14 +5562,14 @@
 D.回避伦理挑战；</t>
         </is>
       </c>
-      <c r="B304" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
+    <row r="304">
+      <c r="A304" t="inlineStr">
         <is>
           <t>00305_单选题
 学习和研究教师伦理学，有助于教师在复杂的道德环境和伦理矛盾中进行正确的（     ）和道德行为选择，从而提高对善恶、是非、荣辱的辨析水平，增强道德自主精神和自控能力。
@@ -5596,14 +5579,14 @@
 D.道德学习；</t>
         </is>
       </c>
-      <c r="B305" t="inlineStr">
+      <c r="B304" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
+    <row r="305">
+      <c r="A305" t="inlineStr">
         <is>
           <t>00306_单选题
 在评价学生表现时，教师应保持什么？（     ）
@@ -5613,14 +5596,14 @@
 D.社会舆论的压力；</t>
         </is>
       </c>
-      <c r="B306" t="inlineStr">
+      <c r="B305" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
+    <row r="306">
+      <c r="A306" t="inlineStr">
         <is>
           <t>00307_单选题
 规范伦理学是（     ）的学科。
@@ -5630,14 +5613,14 @@
 D.研究伦理规范和价值观念；</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
+    <row r="307">
+      <c r="A307" t="inlineStr">
         <is>
           <t>00308_单选题
 下列哪个例子最能体现技术建构论的观点？（     ）
@@ -5647,31 +5630,14 @@
 D.基因编辑技术的突破；</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr">
+      <c r="B307" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>00309_单选题
-关于职业道德的特征的说法正确的是（     ）。
-A.职业道德鲜明的体现了职业特征，表达了特定的职业义务和责任；
-B.这种职业义务和责任主要反映社会的需求，一般不考虑本职业利益；
-C.其内容随时代变化，没有稳定性；
-D.职业道德是一种理论化的道德；</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
+    <row r="308">
+      <c r="A308" t="inlineStr">
         <is>
           <t>00310_单选题
 制度伦理在科研领域的主要作用是什么？（     ）
@@ -5681,14 +5647,14 @@
 D.解决所有科研中的道德难题；</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="311">
-      <c r="A311" t="inlineStr">
+    <row r="309">
+      <c r="A309" t="inlineStr">
         <is>
           <t>00311_单选题
 高校教师在社会服务中如何提升学生的实践能力？（     ）
@@ -5698,14 +5664,14 @@
 D.忽视社会实践；</t>
         </is>
       </c>
-      <c r="B311" t="inlineStr">
+      <c r="B309" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="312">
-      <c r="A312" t="inlineStr">
+    <row r="310">
+      <c r="A310" t="inlineStr">
         <is>
           <t>00312_单选题
 高三学生小明物理成绩不太理想，小明的父母想方设法找到小明的物理老师冯老师家，并希望冯老师周末能到小明家给孩子补课，以每小时300元作为报酬，冯老师以要遵守（     ）的教师道德规范为由拒绝了小明家长。
@@ -5715,14 +5681,14 @@
 D.为人师表；</t>
         </is>
       </c>
-      <c r="B312" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
+    <row r="311">
+      <c r="A311" t="inlineStr">
         <is>
           <t>00313_单选题
 在教师伦理学的实践原则中，（     ）是良好教师伦理建构的首要原则，是每位教育工作者不可动摇的信念。这一准则不仅象征着教师个体对国家和执政党的深切敬仰与忠诚，而且体现了教育事业所承载的重大社会责任与历史担当。
@@ -5732,14 +5698,14 @@
 D.专业敬业；</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
+    <row r="312">
+      <c r="A312" t="inlineStr">
         <is>
           <t>00314_单选题
 教师在处理学生的心理问题时应如何行动？（     ）
@@ -5749,14 +5715,14 @@
 D.避免与学生讨论个人问题；</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
+    <row r="313">
+      <c r="A313" t="inlineStr">
         <is>
           <t>00315_单选题
 （     ）是教师伦理调节功能的内在动力。
@@ -5766,14 +5732,14 @@
 D.目标导向；</t>
         </is>
       </c>
-      <c r="B315" t="inlineStr">
+      <c r="B313" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
+    <row r="314">
+      <c r="A314" t="inlineStr">
         <is>
           <t>00316_单选题
 伦理学致力于回答（     ）这一根本问题。
@@ -5783,14 +5749,14 @@
 D.什么是善？什么是恶？；</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr">
+      <c r="B314" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
+    <row r="315">
+      <c r="A315" t="inlineStr">
         <is>
           <t>00317_单选题
 教师伦理约束功能中的（     ）为教师的行为构建了相应的框架与标尺。
@@ -5800,14 +5766,14 @@
 D.社会监督；</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
+    <row r="316">
+      <c r="A316" t="inlineStr">
         <is>
           <t>00318_单选题
 高校教师在教学过程中应特别关注以下哪项伦理原则？（     ）
@@ -5817,14 +5783,14 @@
 D.只关注科研；</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr">
+      <c r="B316" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="319">
-      <c r="A319" t="inlineStr">
+    <row r="317">
+      <c r="A317" t="inlineStr">
         <is>
           <t>00319_单选题
 高校教师在学术研究中应坚持什么？（     ）
@@ -5834,14 +5800,14 @@
 D.迎合社会舆论；</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
+    <row r="318">
+      <c r="A318" t="inlineStr">
         <is>
           <t>00320_单选题
 教师伦理学不仅是对教师个人道德品质的要求，更是提升（     ）、实现教育公平的关键所在。
@@ -5851,14 +5817,14 @@
 D.教育理想；</t>
         </is>
       </c>
-      <c r="B320" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
+    <row r="319">
+      <c r="A319" t="inlineStr">
         <is>
           <t>00321_单选题
 “产学研结合”模式在高校教师社会服务中主要强调什么？（     ）
@@ -5868,14 +5834,14 @@
 D.社会服务的非盈利性；</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
+    <row r="320">
+      <c r="A320" t="inlineStr">
         <is>
           <t>00322_单选题
 教师的伦理义务不包括以下哪项？（     ）
@@ -5885,14 +5851,14 @@
 D.追求个人利益；</t>
         </is>
       </c>
-      <c r="B322" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
+    <row r="321">
+      <c r="A321" t="inlineStr">
         <is>
           <t>00323_单选题
 （     ）原则是教师伦理学的核心原则之一，其要求教师应秉持公正原则，确保每个学生都能获得平等的教育机会和资源。
@@ -5902,14 +5868,14 @@
 D.爱党爱国；</t>
         </is>
       </c>
-      <c r="B323" t="inlineStr">
+      <c r="B321" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
+    <row r="322">
+      <c r="A322" t="inlineStr">
         <is>
           <t>00324_单选题
 规范伦理学中的伦理原则是指（     ）。
@@ -5919,14 +5885,14 @@
 D.建立起的一套完整的道德规范和判断体系；</t>
         </is>
       </c>
-      <c r="B324" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
+    <row r="323">
+      <c r="A323" t="inlineStr">
         <is>
           <t>00325_单选题
 一般来说，“非升即走”政策主要影响哪类教师群体？（     ）
@@ -5936,14 +5902,14 @@
 D.退休教师；</t>
         </is>
       </c>
-      <c r="B325" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
+    <row r="324">
+      <c r="A324" t="inlineStr">
         <is>
           <t>00326_单选题
 教师道德评价对其道德品质的影响体现在（     ）。
@@ -5953,14 +5919,14 @@
 D.教师道德评价能使教师失去其道德意志；</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
+    <row r="325">
+      <c r="A325" t="inlineStr">
         <is>
           <t>00327_单选题
 在处理学生纠纷时，高校教师应遵循什么原则？（     ）
@@ -5970,14 +5936,14 @@
 D.外部压力；</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B325" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
+    <row r="326">
+      <c r="A326" t="inlineStr">
         <is>
           <t>00328_单选题
 在教师道德规范体系中，（     ）是指那些概括和反映教师道德的主要特征，体现教师道德的根本要求，并成为教师的普遍内心信念，对教师的行为发生影响的基本道德概念。
@@ -5987,14 +5953,14 @@
 D.教师教学规范；</t>
         </is>
       </c>
-      <c r="B328" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
+    <row r="327">
+      <c r="A327" t="inlineStr">
         <is>
           <t>00329_单选题
 伦理信念是（     ）的核心部分，对教师的职业行为有重要影响。
@@ -6004,14 +5970,14 @@
 D.伦理规范；</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
+    <row r="328">
+      <c r="A328" t="inlineStr">
         <is>
           <t>00330_单选题
 教师在与学生建立良好关系时，应首先注重（     ）。
@@ -6021,14 +5987,14 @@
 D.强调自己的主导地位；</t>
         </is>
       </c>
-      <c r="B330" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
+    <row r="329">
+      <c r="A329" t="inlineStr">
         <is>
           <t>00331_单选题
 下列哪项措施不属于夯实制度建设的范畴？（     ）
@@ -6038,14 +6004,14 @@
 D.明确利益冲突管理；</t>
         </is>
       </c>
-      <c r="B331" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
+    <row r="330">
+      <c r="A330" t="inlineStr">
         <is>
           <t>00332_单选题
 不属于教师道德行为评价善恶标准的相对性种类是（     ）。
@@ -6055,14 +6021,14 @@
 D.教师应该承担传播知识、创造知识与监督社会的职责；</t>
         </is>
       </c>
-      <c r="B332" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
+    <row r="331">
+      <c r="A331" t="inlineStr">
         <is>
           <t>00333_单选题
 在教育资源分配中，教师应避免以下哪种做法？（     ）
@@ -6072,14 +6038,14 @@
 D.定期评估分配效果；</t>
         </is>
       </c>
-      <c r="B333" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
+    <row r="332">
+      <c r="A332" t="inlineStr">
         <is>
           <t>00334_单选题
 下列哪项不属于高校教师社会服务伦理建构的文化保障措施？（     ）
@@ -6089,14 +6055,14 @@
 D.表彰社会服务优秀教师；</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
+    <row r="333">
+      <c r="A333" t="inlineStr">
         <is>
           <t>00335_单选题
 教师在处理学生的学术问题时应特别注意什么？（     ）
@@ -6106,14 +6072,14 @@
 D.根据家庭背景决定；</t>
         </is>
       </c>
-      <c r="B335" t="inlineStr">
+      <c r="B333" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
     </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
+    <row r="334">
+      <c r="A334" t="inlineStr">
         <is>
           <t>00336_单选题
 高校教师在教学过程中应如何对待学生的个体差异？（     ）
@@ -6123,14 +6089,14 @@
 D.只关注优秀学生；</t>
         </is>
       </c>
-      <c r="B336" t="inlineStr">
+      <c r="B334" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
     </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
+    <row r="335">
+      <c r="A335" t="inlineStr">
         <is>
           <t>00337_多选题
 下列有关教师人格的看法正确的是（     ）。
@@ -6140,14 +6106,14 @@
 D.是教师在教育活动中表现出的认知、情感、性格等特质；</t>
         </is>
       </c>
-      <c r="B337" t="inlineStr">
+      <c r="B335" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
+    <row r="336">
+      <c r="A336" t="inlineStr">
         <is>
           <t>00338_多选题
 工作绩效评估将教师伦理与具体工作成果紧密结合。不仅关注教学任务，如学生成绩的提升、教学目标的实现等，还深入探究教师在工作过程中的（     ）。
@@ -6157,14 +6123,14 @@
 D.程序；</t>
         </is>
       </c>
-      <c r="B338" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
+    <row r="337">
+      <c r="A337" t="inlineStr">
         <is>
           <t>00339_多选题
 教书育人是教师的天职，主要是因为（     ）。
@@ -6174,14 +6140,14 @@
 D.教书育人概括了教师最根本的社会职责；</t>
         </is>
       </c>
-      <c r="B339" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
+    <row r="338">
+      <c r="A338" t="inlineStr">
         <is>
           <t>00340_多选题
 教师幸福是指处于一定社会经济关系和历史环境的教育工作者，在自觉履行教育教学职责的过程中，由于感受到自身目标和理想的实现而获得的精神层次的满足。以下属于其特征的有（     ）。
@@ -6191,14 +6157,14 @@
 D.具有个体性；</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr">
+      <c r="B338" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
+    <row r="339">
+      <c r="A339" t="inlineStr">
         <is>
           <t>00341_多选题
 高校教师在进行社会服务的过程中遇到的矛盾主要有（     ）。
@@ -6208,14 +6174,14 @@
 D.本职工作与兼职工作的矛盾；</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr">
+      <c r="B339" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
+    <row r="340">
+      <c r="A340" t="inlineStr">
         <is>
           <t>00342_多选题
 在社会的层面上，伦理学（     ）。
@@ -6225,14 +6191,14 @@
 D.强调个体的道德修养与自我完善，鼓励人们通过不断学习与实践来提升自己的道德品质；</t>
         </is>
       </c>
-      <c r="B342" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
+    <row r="341">
+      <c r="A341" t="inlineStr">
         <is>
           <t>00343_多选题
 师生关系伦理的核心在于平等、尊重与和谐这三个维度，其中，和谐体现在师生间的相互（     ）。
@@ -6242,14 +6208,14 @@
 D.信任；</t>
         </is>
       </c>
-      <c r="B343" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
+    <row r="342">
+      <c r="A342" t="inlineStr">
         <is>
           <t>00344_多选题
 教师的主要职责是教书与育人，对教书与育人的关系认识的错误的有（     ）。
@@ -6259,14 +6225,14 @@
 D.教书与育人是一对“教”与“学”双向结合和双边互动的过程；</t>
         </is>
       </c>
-      <c r="B344" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
+    <row r="343">
+      <c r="A343" t="inlineStr">
         <is>
           <t>00345_多选题
 高校教师在日常教学中如何体现教育良心？（     ）
@@ -6276,14 +6242,14 @@
 D.忽视学生的个人背景；</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
+    <row r="344">
+      <c r="A344" t="inlineStr">
         <is>
           <t>00346_多选题
 高校教师在学生管理中应注重哪些方面？（     ）
@@ -6293,14 +6259,14 @@
 D.促进学生心理健康；</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
+    <row r="345">
+      <c r="A345" t="inlineStr">
         <is>
           <t>00347_多选题
 西方教师伦理发展的特点包括？（     ）
@@ -6310,14 +6276,14 @@
 D.在实践和政策制定中发挥了重要作用；</t>
         </is>
       </c>
-      <c r="B347" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
+    <row r="346">
+      <c r="A346" t="inlineStr">
         <is>
           <t>00348_多选题
 习近平指出：“国家繁荣、民族振兴、教育发展，需要我们大力培养造就一支师德高尚、业务精湛、结构合理、充满活力的高素质专业化教师队伍，需要涌现一大批好教师。”一名优秀的教师不仅应该具备扎实的专业知识、一流的专业能力，也要具备良好的师德修养。因此教师必须时刻谨记要不断提高自己的道德修养。对此，下列说法正确的是（     ）。
@@ -6327,14 +6293,14 @@
 D.所有教师在教学中都应该平等地对待每个学生；</t>
         </is>
       </c>
-      <c r="B348" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
+    <row r="347">
+      <c r="A347" t="inlineStr">
         <is>
           <t>00349_多选题
 具备节操道德品质的教师能够（     ）。
@@ -6344,14 +6310,14 @@
 D.始终坚信并完全保持住社会公认的高尚的道德情操；</t>
         </is>
       </c>
-      <c r="B349" t="inlineStr">
+      <c r="B347" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
+    <row r="348">
+      <c r="A348" t="inlineStr">
         <is>
           <t>00350_多选题
 学术研究伦理要求教师应做到（     ）等。
@@ -6361,14 +6327,14 @@
 D.遵循学术规范；</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B348" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
+    <row r="349">
+      <c r="A349" t="inlineStr">
         <is>
           <t>00351_多选题
 下列对教师道德行为与道德品质关系的认识正确的是（     ）。
@@ -6378,14 +6344,14 @@
 D.教师道德行为是一定的道德原则和规范的体现；</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr">
+      <c r="B349" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
+    <row r="350">
+      <c r="A350" t="inlineStr">
         <is>
           <t>00352_多选题
 关于应用伦理学的核心议题——诚实与信任，以下说法正确的有（     ）。
@@ -6395,14 +6361,14 @@
 D.在应用伦理学的理论探讨中，诚实与信任被视为维护社会道德秩序、促进文明进步的重要力量；</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr">
+      <c r="B350" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
+    <row r="351">
+      <c r="A351" t="inlineStr">
         <is>
           <t>00353_多选题
 教师伦理学的使命包括（     ）。
@@ -6412,14 +6378,14 @@
 D.梳理和继承历史上一切有价值的教师道德遗产和资源；</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr">
+      <c r="B351" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
+    <row r="352">
+      <c r="A352" t="inlineStr">
         <is>
           <t>00354_多选题
 教师伦理约束功能中的法律保障具有（     ）。
@@ -6429,14 +6395,14 @@
 D.威慑性；</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
+    <row r="353">
+      <c r="A353" t="inlineStr">
         <is>
           <t>00355_多选题
 科研成果向公众传播时，应关注哪些方面？（     ）
@@ -6446,14 +6412,14 @@
 D.避免误导公众；</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
+    <row r="354">
+      <c r="A354" t="inlineStr">
         <is>
           <t>00356_多选题
 教师伦理学为教育公平的实现提供了伦理保障，是因为（     ）。
@@ -6463,14 +6429,14 @@
 D.教育不仅仅是知识的传递与技能的训练，更是一种人格塑造、价值引领与社会责任培养的过程；</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
+    <row r="355">
+      <c r="A355" t="inlineStr">
         <is>
           <t>00357_多选题
 伦理学的研究对象决定了它的学科特征是（     ）。
@@ -6480,14 +6446,14 @@
 D.伦理学是一门心理科学；</t>
         </is>
       </c>
-      <c r="B357" t="inlineStr">
+      <c r="B355" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
+    <row r="356">
+      <c r="A356" t="inlineStr">
         <is>
           <t>00358_多选题
 关于教师道德行为的结果的论述正确的是（     ）。
@@ -6497,14 +6463,14 @@
 D.行为结果对行为的道德价值具有决定性意义；</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
+    <row r="357">
+      <c r="A357" t="inlineStr">
         <is>
           <t>00359_多选题
 教师公正是指教师在具体的教育教学活动中分配不同的教育资源和调整不同的利益关系时，所表现出的公平和正义。下列现象属于违反教师公正的是（     ）。
@@ -6514,14 +6480,14 @@
 D.教师依据学生的个人兴趣与学习风格，给予不同方式的教育；</t>
         </is>
       </c>
-      <c r="B359" t="inlineStr">
+      <c r="B357" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
+    <row r="358">
+      <c r="A358" t="inlineStr">
         <is>
           <t>00360_多选题
 教师在学术研究中应特别注意哪些方面？（     ）
@@ -6531,14 +6497,14 @@
 D.优先考虑个人利益；</t>
         </is>
       </c>
-      <c r="B360" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
+    <row r="359">
+      <c r="A359" t="inlineStr">
         <is>
           <t>00361_多选题
 在学生管理中，教师应如何体现教育良心？（     ）
@@ -6548,14 +6514,14 @@
 D.根据学生成绩决定处理方式；</t>
         </is>
       </c>
-      <c r="B361" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
+    <row r="360">
+      <c r="A360" t="inlineStr">
         <is>
           <t>00362_多选题
 社会责任伦理要求教师应当将个人的专业知识和技能转化为服务社会的实际行动，具体来说，就是（     ）。
@@ -6565,14 +6531,14 @@
 D.只专注个人科研；</t>
         </is>
       </c>
-      <c r="B362" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
+    <row r="361">
+      <c r="A361" t="inlineStr">
         <is>
           <t>00363_多选题
 教师在道德修养过程中，学习的内容包括（     ）。
@@ -6582,14 +6548,14 @@
 D.学习伦理道德知识；</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
+    <row r="362">
+      <c r="A362" t="inlineStr">
         <is>
           <t>00364_多选题
 徐特立关于教师的观点包括：（     ）。
@@ -6599,14 +6565,14 @@
 D.认为优秀教师应结合“经师”和“人师”角色；</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr">
+      <c r="B362" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
+    <row r="363">
+      <c r="A363" t="inlineStr">
         <is>
           <t>00365_多选题
 高校教师参与创新创业活动的优势包括（     ）？
@@ -6616,14 +6582,14 @@
 D.能够有效将科研成果转化为实际应用；</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr">
+      <c r="B363" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="364">
+      <c r="A364" t="inlineStr">
         <is>
           <t>00366_多选题
 关于教师道德评价对教师道德意识和活动的影响，认识正确的是（     ）。
@@ -6633,14 +6599,14 @@
 D.教师道德评价在教师道德认识和教师职业道德行为不断转化中起着媒介作用；</t>
         </is>
       </c>
-      <c r="B366" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+    <row r="365">
+      <c r="A365" t="inlineStr">
         <is>
           <t>00367_多选题
 技术中性论的观点包含哪些内容？（     ）
@@ -6650,14 +6616,14 @@
 D.技术遵循提升效率的统一标准；</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr">
+      <c r="B365" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
+    <row r="366">
+      <c r="A366" t="inlineStr">
         <is>
           <t>00368_多选题
 高校教师社会服务历史演变中的重要里程碑包括（     ）？
@@ -6667,14 +6633,14 @@
 D.教师收入水平的普遍增长；</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
+    <row r="367">
+      <c r="A367" t="inlineStr">
         <is>
           <t>00369_多选题
 教师伦理的功能主要包括（     ）。
@@ -6684,14 +6650,14 @@
 D.约束功能；</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr">
+      <c r="B367" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
+    <row r="368">
+      <c r="A368" t="inlineStr">
         <is>
           <t>00370_多选题
 处于他律与自律统一机制的教师，在与教师道德规范体系的关系上，体现的特点是（     ）。
@@ -6701,14 +6667,14 @@
 D.教师与教师道德规范体系已经浑然一体，达到“从心所欲不逾矩”的道德境界；</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr">
+      <c r="B368" t="inlineStr">
         <is>
           <t>BD</t>
         </is>
       </c>
     </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
+    <row r="369">
+      <c r="A369" t="inlineStr">
         <is>
           <t>00371_多选题
 21世纪以来，教师伦理专业化的发展方向包括：（     ）。
@@ -6718,14 +6684,14 @@
 D.友好的师生关系；</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr">
+      <c r="B369" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
+    <row r="370">
+      <c r="A370" t="inlineStr">
         <is>
           <t>00372_多选题
 教师道德的社会作用主要包括（     ）。
@@ -6735,14 +6701,14 @@
 D.有利于促进社会道德环境优化和人类文明进步；</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
+    <row r="371">
+      <c r="A371" t="inlineStr">
         <is>
           <t>00373_多选题
 教师在使用网络平台进行教学时应遵守的伦理准则包括（     ）。
@@ -6752,14 +6718,14 @@
 D.不发布与教学无关的内容；</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>00374_多选题
 资源保障如何助力高校教师有效开展社会服务活动？（     ）
@@ -6769,14 +6735,14 @@
 D.替代教师在服务中的核心作用；</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr">
+      <c r="B372" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
+    <row r="373">
+      <c r="A373" t="inlineStr">
         <is>
           <t>00375_多选题
 21世纪之后，教师伦理发展的特点包括：（     ）。
@@ -6786,14 +6752,14 @@
 D.教师行为规范转向强调专业伦理；</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
+      <c r="B373" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
+    <row r="374">
+      <c r="A374" t="inlineStr">
         <is>
           <t>00376_多选题
 教师道德公正就是指教师在职业活动中处理人与人之间的关系和各种事情时能做到坚持原则、为人正直，公平合理地对待和评价全体合作者。影响教师道德公正观念的因素有（     ）。
@@ -6803,14 +6769,14 @@
 D.教师对每个学生的认识；</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
+      <c r="B374" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>00377_多选题
 教师道德评价的功能包括（     ）。
@@ -6820,14 +6786,14 @@
 D.加强教师道德评价，是建立良好校风校纪的重要途径；</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
+    <row r="376">
+      <c r="A376" t="inlineStr">
         <is>
           <t>00378_多选题
 教学过程中的伦理矛盾主要体现为（     ）。
@@ -6837,14 +6803,14 @@
 D.教师对教学工作的态度和责任心不能满足教学工作要求引起的矛盾；</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr">
+      <c r="B376" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
+    <row r="377">
+      <c r="A377" t="inlineStr">
         <is>
           <t>00379_多选题
 教师在建立良好的师生关系时，需要做到（     ）。
@@ -6854,14 +6820,14 @@
 D.促进学生全面发展；</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="378">
+      <c r="A378" t="inlineStr">
         <is>
           <t>00380_多选题
 影响师生伦理关系的主要因素表现（     ）。
@@ -6871,14 +6837,14 @@
 D.师生交往的时空、性别等因素；</t>
         </is>
       </c>
-      <c r="B380" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="379">
+      <c r="A379" t="inlineStr">
         <is>
           <t>00381_多选题
 在实践基础上加强教师道德建设的途径有（     ）。
@@ -6888,14 +6854,14 @@
 D.拓展师德建设途径；</t>
         </is>
       </c>
-      <c r="B381" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
+    <row r="380">
+      <c r="A380" t="inlineStr">
         <is>
           <t>00382_多选题
 富有成效的教育环境包括（     ）。
@@ -6905,14 +6871,14 @@
 D.科学研究；</t>
         </is>
       </c>
-      <c r="B382" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
+    <row r="381">
+      <c r="A381" t="inlineStr">
         <is>
           <t>00383_多选题
 关于教师职业道德规范，下列说法错误的是（     ）。
@@ -6922,14 +6888,14 @@
 D.教师根据学生的实际特点与学习能力进行不同的教育，违背了教育民主原则；</t>
         </is>
       </c>
-      <c r="B383" t="inlineStr">
+      <c r="B381" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
+    <row r="382">
+      <c r="A382" t="inlineStr">
         <is>
           <t>00384_多选题
 教师荣誉是社会对教师教学行为所做的肯定性评价，以及教师由此产生的自我认同。下列措施有利于提高教师荣誉的有（     ）。
@@ -6939,14 +6905,14 @@
 D.正确处理好自尊与谦逊的关系；</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
+    <row r="383">
+      <c r="A383" t="inlineStr">
         <is>
           <t>00385_多选题
 教师职业道德的特征主要表现在（     ）。
@@ -6956,14 +6922,14 @@
 D.在道德影响上，教师道德比其他职业道德更广泛、更深远；</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr">
+      <c r="B383" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
+    <row r="384">
+      <c r="A384" t="inlineStr">
         <is>
           <t>00386_多选题
 高校教师科研伦理规范中，以下哪些属于学术诚信的范畴？（     ）
@@ -6973,14 +6939,14 @@
 D.引用他人工作时进行正确标注；</t>
         </is>
       </c>
-      <c r="B386" t="inlineStr">
+      <c r="B384" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
+    <row r="385">
+      <c r="A385" t="inlineStr">
         <is>
           <t>00387_多选题
 下列属于教师道德范畴的有（     ）。
@@ -6990,14 +6956,14 @@
 D.道德良心；</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr">
+      <c r="B385" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
+    <row r="386">
+      <c r="A386" t="inlineStr">
         <is>
           <t>00388_多选题
 如何正确对待教师道德荣誉（     ）。
@@ -7007,14 +6973,14 @@
 D.划清荣誉感和虚荣心的界限；</t>
         </is>
       </c>
-      <c r="B388" t="inlineStr">
+      <c r="B386" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
+    <row r="387">
+      <c r="A387" t="inlineStr">
         <is>
           <t>00389_多选题
 师生关系伦理的核心在于平等、尊重与和谐这三个维度，其中，尊重是对学生（     ）的珍视。
@@ -7024,14 +6990,14 @@
 D.思想观点；</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
+      <c r="B387" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
+    <row r="388">
+      <c r="A388" t="inlineStr">
         <is>
           <t>00390_多选题
 处于道德品质形成与发展的第二阶段的教师（     ）。
@@ -7041,14 +7007,14 @@
 D.他们的道德认识、情感、意志都处于消极、被动状态；</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
+    <row r="389">
+      <c r="A389" t="inlineStr">
         <is>
           <t>00391_多选题
 教师在研究中应如何确保教育良心的实践？（     ）
@@ -7058,14 +7024,14 @@
 D.只关注发表数量；</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="390">
+      <c r="A390" t="inlineStr">
         <is>
           <t>00392_多选题
 师德养成的一般路径包括（     ）。
@@ -7075,14 +7041,14 @@
 D.教学品质；</t>
         </is>
       </c>
-      <c r="B392" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+    <row r="391">
+      <c r="A391" t="inlineStr">
         <is>
           <t>00393_多选题
 教师道德规范体系对教师职业行为的影响和作用的机制主要有（     ）。
@@ -7092,14 +7058,14 @@
 D.教师道德他律与自律相统一；</t>
         </is>
       </c>
-      <c r="B393" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
+    <row r="392">
+      <c r="A392" t="inlineStr">
         <is>
           <t>00394_多选题
 韩愈对教师职业道德的贡献包括：（     ）。
@@ -7109,14 +7075,14 @@
 D.忽视教师的道德修养；</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
+      <c r="B392" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
+    <row r="393">
+      <c r="A393" t="inlineStr">
         <is>
           <t>00395_多选题
 在教学过程中，教师应如何实践教育良心？（     ）
@@ -7126,14 +7092,14 @@
 D.根据个人偏好处理事务；</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
+    <row r="394">
+      <c r="A394" t="inlineStr">
         <is>
           <t>00396_多选题
 进入21世纪，随着全球化的深入发展和信息技术的广泛应用，应用伦理学的研究领域进一步拓展，涵盖了（     ）等众多新兴领域
@@ -7143,14 +7109,14 @@
 D.商业伦理；</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
+    <row r="395">
+      <c r="A395" t="inlineStr">
         <is>
           <t>00397_多选题
 教师伦理学的实践原则——专业敬业，要求教师（     ）。
@@ -7160,14 +7126,14 @@
 D.按照职业伦理道德规范，积极参与教育科研与学术交流活动，不断提升自己的专业素养与创新能力，为教育事业的发展贡献自己的力量；</t>
         </is>
       </c>
-      <c r="B397" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
+    <row r="396">
+      <c r="A396" t="inlineStr">
         <is>
           <t>00398_多选题
 学术保障在高校教师社会服务伦理建构中的体现有（     ）？
@@ -7177,14 +7143,14 @@
 D.单纯扩大教师社会服务的范围与数量；</t>
         </is>
       </c>
-      <c r="B398" t="inlineStr">
+      <c r="B396" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
+    <row r="397">
+      <c r="A397" t="inlineStr">
         <is>
           <t>00399_多选题
 宋元明清时期，教师职业道德的特点包括：（     ）。
@@ -7194,14 +7160,14 @@
 D.教师要“正言”“正行”“正教”；</t>
         </is>
       </c>
-      <c r="B399" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t>00400_多选题
 师生关系伦理倡导的是一种基于（     ）的互动模式。
@@ -7211,14 +7177,14 @@
 D.和谐；</t>
         </is>
       </c>
-      <c r="B400" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
+    <row r="399">
+      <c r="A399" t="inlineStr">
         <is>
           <t>00401_多选题
 制度保障在高校教师社会服务伦理建构中的关键作用包括（     ）？
@@ -7228,14 +7194,14 @@
 D.加强社会服务技能培训；</t>
         </is>
       </c>
-      <c r="B401" t="inlineStr">
+      <c r="B399" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
+    <row r="400">
+      <c r="A400" t="inlineStr">
         <is>
           <t>00402_多选题
 中西方教师伦理研究发展的未来趋势包括？（     ）
@@ -7245,14 +7211,14 @@
 D.教师伦理专业发展对学生的品格和价值观的塑造；</t>
         </is>
       </c>
-      <c r="B402" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
+    <row r="401">
+      <c r="A401" t="inlineStr">
         <is>
           <t>00403_多选题
 教师道德行为的社会评价形式有（     ）。
@@ -7262,14 +7228,14 @@
 D.社会舆论；</t>
         </is>
       </c>
-      <c r="B403" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
+    <row r="402">
+      <c r="A402" t="inlineStr">
         <is>
           <t>00404_多选题
 梁启超关于教师的观点包括：（     ）。
@@ -7279,14 +7245,14 @@
 D.忽视教师的个人得失；</t>
         </is>
       </c>
-      <c r="B404" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
+    <row r="403">
+      <c r="A403" t="inlineStr">
         <is>
           <t>00405_多选题
 教师坚持以人为本体现在（     ）。
@@ -7296,14 +7262,14 @@
 D.尊重学生；</t>
         </is>
       </c>
-      <c r="B405" t="inlineStr">
+      <c r="B403" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="404">
+      <c r="A404" t="inlineStr">
         <is>
           <t>00406_多选题
 制度伦理在科研中的实现方式包括哪些？（     ）
@@ -7313,14 +7279,14 @@
 D.尊老爱幼；</t>
         </is>
       </c>
-      <c r="B406" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="405">
+      <c r="A405" t="inlineStr">
         <is>
           <t>00407_多选题
 教师伦理学认为教育公平的实现需要教师（     ）。
@@ -7330,14 +7296,14 @@
 D.确保教育机会对每一位学生的平等开放；</t>
         </is>
       </c>
-      <c r="B407" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
+    <row r="406">
+      <c r="A406" t="inlineStr">
         <is>
           <t>00408_多选题
 下列属于在教师与他遵守的原则和规范之间发挥支配作用的中介力量是（     ）。
@@ -7347,14 +7313,14 @@
 D.内心信念；</t>
         </is>
       </c>
-      <c r="B408" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
+    <row r="407">
+      <c r="A407" t="inlineStr">
         <is>
           <t>00409_多选题
 与教育职业活动的一般特点相比，高校教师职业活动的特殊性主要表现在（     ）。
@@ -7364,14 +7330,14 @@
 D.教育活动在时空上具有一定弹性和自由度；</t>
         </is>
       </c>
-      <c r="B409" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
+    <row r="408">
+      <c r="A408" t="inlineStr">
         <is>
           <t>00410_多选题
 下列有关理想人格的论述正确的是（     ）。
@@ -7381,14 +7347,14 @@
 D.理想人格会因不同时代等因素而不同；</t>
         </is>
       </c>
-      <c r="B410" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
+    <row r="409">
+      <c r="A409" t="inlineStr">
         <is>
           <t>00411_多选题
 高校教师社会服务的价值意蕴体现在以下哪些方面？（     ）
@@ -7398,14 +7364,14 @@
 D.加强高校与社会的联系；</t>
         </is>
       </c>
-      <c r="B411" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
+    <row r="410">
+      <c r="A410" t="inlineStr">
         <is>
           <t>00412_多选题
 教师伦理学的实践原则——公正无私，要求教师（     ）。
@@ -7415,14 +7381,14 @@
 D.确保每个学生都能获得平等的教育机会和资源。这意味着在评价学生、分配教学资源时，教师应不受个人喜好、偏见或外部压力的影响，坚持客观、公正的标准；</t>
         </is>
       </c>
-      <c r="B412" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
+    <row r="411">
+      <c r="A411" t="inlineStr">
         <is>
           <t>00413_多选题
 高校教师之所以要具有学术研究伦理，是因为坚守学术伦理，能够（     ）。
@@ -7432,14 +7398,14 @@
 D.为学生树立榜样，培养出高尚品德和扎实学识的优秀人才；</t>
         </is>
       </c>
-      <c r="B413" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
+    <row r="412">
+      <c r="A412" t="inlineStr">
         <is>
           <t>00414_多选题
 有效的自我约束可以帮助教师（     ）。
@@ -7449,14 +7415,14 @@
 D.为学生树立起良好的道德榜样；</t>
         </is>
       </c>
-      <c r="B414" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
+    <row r="413">
+      <c r="A413" t="inlineStr">
         <is>
           <t>00415_多选题
 高校教师在制定课程评价标准时，应遵循哪些原则？（     ）
@@ -7466,14 +7432,14 @@
 D.评价标准的一致性；</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
+      <c r="B413" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
+    <row r="414">
+      <c r="A414" t="inlineStr">
         <is>
           <t>00416_多选题
 教师伦理约束功能中的社会监督的具体方式有（     ）。
@@ -7483,14 +7449,14 @@
 D.家长参与；</t>
         </is>
       </c>
-      <c r="B416" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
+    <row r="415">
+      <c r="A415" t="inlineStr">
         <is>
           <t>00417_多选题
 对教师道德行为的动机理解正确的是（     ）。
@@ -7500,14 +7466,14 @@
 D.形式是指没有外化为实际行为的动机；</t>
         </is>
       </c>
-      <c r="B417" t="inlineStr">
+      <c r="B415" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>00418_多选题
 学术研究伦理学术伦理要求教师应遵循学术规范，包括（     ）等。
@@ -7517,14 +7483,14 @@
 D.成果发表的正当性；</t>
         </is>
       </c>
-      <c r="B418" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>00419_多选题
 以下哪些措施有助于缓解教师面临的科研与教学双重压力？（     ）
@@ -7534,14 +7500,14 @@
 D.强化对学生自主学习能力的培养；</t>
         </is>
       </c>
-      <c r="B419" t="inlineStr">
+      <c r="B417" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
+    <row r="418">
+      <c r="A418" t="inlineStr">
         <is>
           <t>00420_多选题
 高校教师价值观是（     ）。
@@ -7551,31 +7517,14 @@
 D.是促进社会发展的力量；</t>
         </is>
       </c>
-      <c r="B420" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>00421_多选题
-下列哪一项是教师职业道德修养的最终目的？（     ）（该题目已移除！）
-A.培养良好职业道德认知；
-B.培养良好职业道德情感；
-C.培养良好职业道德意志；
-D.培养良好职业道德行为；</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
+    <row r="419">
+      <c r="A419" t="inlineStr">
         <is>
           <t>00422_多选题
 教师职业道德行为的构成要素，从大处至少包括（     ）。
@@ -7585,14 +7534,14 @@
 D.教师道德行为的结果；</t>
         </is>
       </c>
-      <c r="B422" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
+    <row r="420">
+      <c r="A420" t="inlineStr">
         <is>
           <t>00423_多选题
 教育教学伦理要求教师在传授知识的同时，必须（     ），以促进学生全面而个性化的发展。
@@ -7602,14 +7551,14 @@
 D.采用科学、合理的教学方法和手段；</t>
         </is>
       </c>
-      <c r="B423" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
+    <row r="421">
+      <c r="A421" t="inlineStr">
         <is>
           <t>00424_多选题
 孔子对教师的要求包括以下哪些方面？（     ）
@@ -7619,14 +7568,14 @@
 D.不叩亦鸣；</t>
         </is>
       </c>
-      <c r="B424" t="inlineStr">
+      <c r="B421" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
+    <row r="422">
+      <c r="A422" t="inlineStr">
         <is>
           <t>00425_多选题
 规范伦理学是研究伦理规范和价值观念的学科，其主要包括（     ）等方面的研究。
@@ -7636,14 +7585,14 @@
 D.道德规范；</t>
         </is>
       </c>
-      <c r="B425" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
+    <row r="423">
+      <c r="A423" t="inlineStr">
         <is>
           <t>00426_多选题
 教师职业道德的社会作用主要有（     ）。
@@ -7653,31 +7602,14 @@
 D.有利于促进社会道德环境优化和人类文明进步；</t>
         </is>
       </c>
-      <c r="B426" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>00427_多选题
-作为研究如何应用伦理原则和道德规范来解决实际问题的学科，应用伦理学是对社会生活各领域进行道德审视的科学。（     ）其。（该题目已移除！）
-A.指导人们道德行为的基本原则，如权利原则、善恶原则等；
-B.作为一种程序伦理，是民主时代的道德理论，体现了民主原则在道德哲学中的运用；
-C.主要包括伦理学的起源、伦理学的语言和伦理学的方法等方面的研究；
-D.渗透着强烈的价值理念或价值意涵，具体表现为其体现了在以自由、自主性为导向的民主法治时代现代伦理学建构的逻辑法则；</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>BD</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
+    <row r="424">
+      <c r="A424" t="inlineStr">
         <is>
           <t>00428_多选题
 生物技术革命主要体现在哪些方面？（     ）
@@ -7687,14 +7619,14 @@
 D.生物医药；</t>
         </is>
       </c>
-      <c r="B428" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
+    <row r="425">
+      <c r="A425" t="inlineStr">
         <is>
           <t>00429_多选题
 有关师德教育和师德修养关系说法正确的是（     ）。
@@ -7704,14 +7636,14 @@
 D.二者都是致力于教师道德养成；</t>
         </is>
       </c>
-      <c r="B429" t="inlineStr">
+      <c r="B425" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
+    <row r="426">
+      <c r="A426" t="inlineStr">
         <is>
           <t>00430_多选题
 教师伦理学的实践原则——尊重学生，要求教师（     ）。
@@ -7721,14 +7653,14 @@
 D.避免任何形式的歧视与偏见，确保每个学生都能在公平、公正的环境中成长，实现自我价值；</t>
         </is>
       </c>
-      <c r="B430" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
+    <row r="427">
+      <c r="A427" t="inlineStr">
         <is>
           <t>00431_多选题
 苏格拉底关于教师伦理的观点包括：（     ）。
@@ -7738,14 +7670,14 @@
 D.强调“道德可教”；</t>
         </is>
       </c>
-      <c r="B431" t="inlineStr">
+      <c r="B427" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
+    <row r="428">
+      <c r="A428" t="inlineStr">
         <is>
           <t>00432_多选题
 关于应用伦理学的核心议题——公正与平等，以下说法正确的有（     ）。
@@ -7755,31 +7687,14 @@
 D.平等，则强调个体或群体在享有权利、承担义务时应得到同等的对待与尊重。公正与平等的理论探讨，旨在构建一个更加和谐、包容、可持续的社会环境；</t>
         </is>
       </c>
-      <c r="B432" t="inlineStr">
+      <c r="B428" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>00433_多选题
-教师在履行教育教学义务的过程中，最主要、最基本的道德责任是（     ）。（该题目已移除！）
-A.依法执教；
-B.教书育人；
-C.爱岗敬业；
-D.团结协作；</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
+    <row r="429">
+      <c r="A429" t="inlineStr">
         <is>
           <t>00434_多选题
 教师伦理的调节功能主要包括（     ）。
@@ -7789,14 +7704,14 @@
 D.物质激励；</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
+    <row r="430">
+      <c r="A430" t="inlineStr">
         <is>
           <t>00435_多选题
 虚假信息传播可能带来的后果包括哪些？（     ）
@@ -7806,14 +7721,14 @@
 D.可能引发社会问题和舆论误导；</t>
         </is>
       </c>
-      <c r="B435" t="inlineStr">
+      <c r="B430" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
+    <row r="431">
+      <c r="A431" t="inlineStr">
         <is>
           <t>00436_多选题
 孟子关于教师的哪些观点是正确的？（     ）
@@ -7823,14 +7738,14 @@
 D.重视教师自身修养；</t>
         </is>
       </c>
-      <c r="B436" t="inlineStr">
+      <c r="B431" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
+    <row r="432">
+      <c r="A432" t="inlineStr">
         <is>
           <t>00437_多选题
 高校教师如何通过师生关系体现教育良心？（     ）
@@ -7840,14 +7755,14 @@
 D.关注学生的全面发展；</t>
         </is>
       </c>
-      <c r="B437" t="inlineStr">
+      <c r="B432" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
+    <row r="433">
+      <c r="A433" t="inlineStr">
         <is>
           <t>00438_多选题
 教师伦理约束功能中的制度约束是通过制定详尽的教师职业道德规范体系及相关制度，这些制度需要考虑到（     ）。
@@ -7857,14 +7772,14 @@
 D.教学质量的目标要求；</t>
         </is>
       </c>
-      <c r="B438" t="inlineStr">
+      <c r="B433" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
+    <row r="434">
+      <c r="A434" t="inlineStr">
         <is>
           <t>00439_多选题
 教师道德公正的构成要素主要包括（     ）。
@@ -7874,14 +7789,14 @@
 D.赏罚分明；</t>
         </is>
       </c>
-      <c r="B439" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="440">
-      <c r="A440" t="inlineStr">
+    <row r="435">
+      <c r="A435" t="inlineStr">
         <is>
           <t>00440_多选题
 教师道德良心对教师行为的作用表现在（     ）。
@@ -7891,14 +7806,14 @@
 D.在教师行为结束之后，起着自我评价的作用；</t>
         </is>
       </c>
-      <c r="B440" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
+    <row r="436">
+      <c r="A436" t="inlineStr">
         <is>
           <t>00441_多选题
 高校教师在课程设计时应考虑哪些因素？（     ）
@@ -7908,14 +7823,14 @@
 D.课程的评估方式；</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B436" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
+    <row r="437">
+      <c r="A437" t="inlineStr">
         <is>
           <t>00442_多选题
 德谟克里特关于教师道德的观点包括：（     ）。
@@ -7925,14 +7840,14 @@
 D.教育应基于鼓励和说服；</t>
         </is>
       </c>
-      <c r="B442" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
+    <row r="438">
+      <c r="A438" t="inlineStr">
         <is>
           <t>00443_多选题
 关于教师的角色自我和个性自我的认识正确的是（     ）。
@@ -7942,14 +7857,14 @@
 D.要求教师讲角色审美化、个性化、感情化、情感化；</t>
         </is>
       </c>
-      <c r="B443" t="inlineStr">
+      <c r="B438" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
+    <row r="439">
+      <c r="A439" t="inlineStr">
         <is>
           <t>00444_多选题
 关于应用伦理学的核心议题——权利与权益，以下说法正确的有（     ）。
@@ -7959,14 +7874,14 @@
 D.其要求我们在尊重个体权利的同时，也要考虑到社会整体利益与长远利益的重要性，通过理性的对话与协商，寻求各方都能接受的解决方案；</t>
         </is>
       </c>
-      <c r="B444" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
+    <row r="440">
+      <c r="A440" t="inlineStr">
         <is>
           <t>00445_多选题
 教师伦理学何以促进社会的文明与进步（     ）。
@@ -7976,14 +7891,14 @@
 D.专注于提高学生的升学率；</t>
         </is>
       </c>
-      <c r="B445" t="inlineStr">
+      <c r="B440" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
+    <row r="441">
+      <c r="A441" t="inlineStr">
         <is>
           <t>00446_多选题
 哪些因素共同促进了高校教师社会服务的发展？（     ）
@@ -7993,14 +7908,14 @@
 D.高校内部丰富的学术研究成果作为基础；</t>
         </is>
       </c>
-      <c r="B446" t="inlineStr">
+      <c r="B441" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>00447_多选题
 社会保障在高校教师社会服务伦理建构中的作用主要体现在（     ）？
@@ -8010,14 +7925,14 @@
 D.通过多方参与形成联动的社会服务网络与支持体系；</t>
         </is>
       </c>
-      <c r="B447" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>CD</t>
         </is>
       </c>
     </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>00448_多选题
 社会责任伦理是高校教师不可或缺的重要品质，原因在于（     ）。
@@ -8027,14 +7942,14 @@
 D.增强教师的职业幸福感与成就感；</t>
         </is>
       </c>
-      <c r="B448" t="inlineStr">
+      <c r="B443" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
+    <row r="444">
+      <c r="A444" t="inlineStr">
         <is>
           <t>00449_多选题
 教师道德品质具有哪些特征（     ）。
@@ -8044,14 +7959,14 @@
 D.教师道德品质是在“行为整体”中表现出来的稳定特征和倾向；</t>
         </is>
       </c>
-      <c r="B449" t="inlineStr">
+      <c r="B444" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
+    <row r="445">
+      <c r="A445" t="inlineStr">
         <is>
           <t>00450_多选题
 在个人的层面上，伦理学（     ）。
@@ -8061,14 +7976,14 @@
 D.强调个体的道德修养与自我完善，鼓励人们通过不断学习与实践来提升自己的道德品质；</t>
         </is>
       </c>
-      <c r="B450" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
+    <row r="446">
+      <c r="A446" t="inlineStr">
         <is>
           <t>00451_多选题
 教师道德的一般功能有（     ）。
@@ -8078,14 +7993,14 @@
 D.激励功能；</t>
         </is>
       </c>
-      <c r="B451" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
+    <row r="447">
+      <c r="A447" t="inlineStr">
         <is>
           <t>00452_多选题
 教师在处理师生关系时应遵循哪些伦理原则？（     ）
@@ -8095,14 +8010,14 @@
 D.依据学生的家庭背景决定；</t>
         </is>
       </c>
-      <c r="B452" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
+    <row r="448">
+      <c r="A448" t="inlineStr">
         <is>
           <t>00453_多选题
 合作研究中应如何确保公正性？（     ）
@@ -8112,14 +8027,14 @@
 D.追求最大经济收益；</t>
         </is>
       </c>
-      <c r="B453" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
+    <row r="449">
+      <c r="A449" t="inlineStr">
         <is>
           <t>00454_多选题
 18世纪末至20世纪初，教师伦理学的发展特点包括：（     ）。
@@ -8129,14 +8044,14 @@
 D.赫尔巴特强调教师的自我修养；</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B449" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
+    <row r="450">
+      <c r="A450" t="inlineStr">
         <is>
           <t>00455_多选题
 教师的某一行为的分析角度有（     ）。
@@ -8146,14 +8061,14 @@
 D.政治学角度；</t>
         </is>
       </c>
-      <c r="B455" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
+    <row r="451">
+      <c r="A451" t="inlineStr">
         <is>
           <t>00456_多选题
 拓展师德建设的途径有（     ）。
@@ -8163,14 +8078,14 @@
 D.将教学评价纳入培训体系；</t>
         </is>
       </c>
-      <c r="B456" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
+    <row r="452">
+      <c r="A452" t="inlineStr">
         <is>
           <t>00457_多选题
 教育良心在科研指导中要求教师做到哪些？（     ）
@@ -8180,14 +8095,14 @@
 D.维护学术诚信；</t>
         </is>
       </c>
-      <c r="B457" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
+    <row r="453">
+      <c r="A453" t="inlineStr">
         <is>
           <t>00458_多选题
 教师伦理学为教育质量的提升提供了伦理基础，是因为（     ）。
@@ -8197,14 +8112,14 @@
 D.教师伦理学要求关注每一位学生的成绩；</t>
         </is>
       </c>
-      <c r="B458" t="inlineStr">
+      <c r="B453" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
+    <row r="454">
+      <c r="A454" t="inlineStr">
         <is>
           <t>00459_多选题
 “热爱教育、忠诚教育”作为教师道德原则的基本原则的具体要求有（     ）。
@@ -8214,31 +8129,14 @@
 D.较高的学历；</t>
         </is>
       </c>
-      <c r="B459" t="inlineStr">
+      <c r="B454" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>00460_多选题
-教师道德作为种特殊的意识形态系统，主要由以下要素构成（     ）。（该题目已移除！）
-A.教师道德意识现象；
-B.教师道德关系现象；
-C.教师道德规范现象；
-D.教师道德活动现象；</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>ABCD</t>
-        </is>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
+    <row r="455">
+      <c r="A455" t="inlineStr">
         <is>
           <t>00461_多选题
 以下关于教师道德教育的说法正确的是（     ）。
@@ -8248,14 +8146,14 @@
 D.改革创新，师德教育的理念；</t>
         </is>
       </c>
-      <c r="B461" t="inlineStr">
+      <c r="B455" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
+    <row r="456">
+      <c r="A456" t="inlineStr">
         <is>
           <t>00462_多选题
 内心信念在教师道德评价中的作用主要表现为（     ）。
@@ -8265,14 +8163,14 @@
 D.它是实现教师道德评价成效的途径和目的；</t>
         </is>
       </c>
-      <c r="B462" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
+    <row r="457">
+      <c r="A457" t="inlineStr">
         <is>
           <t>00463_多选题
 关于教师职业道德规范，下列说法正确的是（     ）。
@@ -8282,14 +8180,14 @@
 D.爱国守法是教师职业道德的本质要求；</t>
         </is>
       </c>
-      <c r="B463" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
+    <row r="458">
+      <c r="A458" t="inlineStr">
         <is>
           <t>00464_多选题
 高校教师在社会服务中可能面临的多重挑战包括（     ）？
@@ -8299,14 +8197,14 @@
 D.如何在公众中建立并维护信任与公信力；</t>
         </is>
       </c>
-      <c r="B464" t="inlineStr">
+      <c r="B458" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
+    <row r="459">
+      <c r="A459" t="inlineStr">
         <is>
           <t>00465_多选题
 墨子对教师的要求有哪些？（     ）
@@ -8316,14 +8214,14 @@
 D.积极教育；</t>
         </is>
       </c>
-      <c r="B465" t="inlineStr">
+      <c r="B459" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
+    <row r="460">
+      <c r="A460" t="inlineStr">
         <is>
           <t>00466_多选题
 教师道德荣誉的作用主要有（     ）。
@@ -8333,14 +8231,14 @@
 D.激励教师的奋发精神，调动教师潜能；</t>
         </is>
       </c>
-      <c r="B466" t="inlineStr">
+      <c r="B460" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
+    <row r="461">
+      <c r="A461" t="inlineStr">
         <is>
           <t>00467_多选题
 教师伦理学的实践原则——关爱学生，要求教师（     ）。
@@ -8350,14 +8248,14 @@
 D.积极为学生提供必要的帮助与支持，如心理疏导、学习辅导等，以促进学生的健康成长与全面发展；</t>
         </is>
       </c>
-      <c r="B467" t="inlineStr">
+      <c r="B461" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
+    <row r="462">
+      <c r="A462" t="inlineStr">
         <is>
           <t>00468_多选题
 教师伦理的约束功能，包括（     ）。
@@ -8367,14 +8265,14 @@
 D.社会监督；</t>
         </is>
       </c>
-      <c r="B468" t="inlineStr">
+      <c r="B462" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
+    <row r="463">
+      <c r="A463" t="inlineStr">
         <is>
           <t>00469_多选题
 教师伦理学认为教师应当如何在教育教学中确保正确的政治方向（     ）。
@@ -8384,14 +8282,14 @@
 D.将党的相关政策方针运用到日常教学实践当中；</t>
         </is>
       </c>
-      <c r="B469" t="inlineStr">
+      <c r="B463" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
+    <row r="464">
+      <c r="A464" t="inlineStr">
         <is>
           <t>00470_多选题
 教师伦理的激励功能，涉及（     ）维度。
@@ -8401,31 +8299,14 @@
 D.荣誉；</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B464" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>00471_多选题
-张桂梅老师一生清贫，坚守三尺讲台。这突出体现了张桂梅老师的（     ）。（该题目已移除！）
-A.道德认知；
-B.道德情感；
-C.道德意志；
-D.道德行为；</t>
-        </is>
-      </c>
-      <c r="B471" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
+    <row r="465">
+      <c r="A465" t="inlineStr">
         <is>
           <t>00472_多选题
 有关内省这种师德修养方法的的认识正确的是（     ）。
@@ -8435,14 +8316,14 @@
 D.内省有助于教师培养良好的个性品德；</t>
         </is>
       </c>
-      <c r="B472" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>BCD</t>
         </is>
       </c>
     </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
+    <row r="466">
+      <c r="A466" t="inlineStr">
         <is>
           <t>00473_多选题
 科研过程中的透明性体现在哪些方面？（     ）
@@ -8452,14 +8333,14 @@
 D.研究机密的公开；</t>
         </is>
       </c>
-      <c r="B473" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
+    <row r="467">
+      <c r="A467" t="inlineStr">
         <is>
           <t>00474_多选题
 教师在教学设计中应考虑哪些因素？（     ）
@@ -8469,14 +8350,14 @@
 D.教学资源的分配；</t>
         </is>
       </c>
-      <c r="B474" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
+    <row r="468">
+      <c r="A468" t="inlineStr">
         <is>
           <t>00475_多选题
 教师在培养教育良心过程中应关注哪些方面？（     ）
@@ -8486,14 +8367,14 @@
 D.科研成果的数量；</t>
         </is>
       </c>
-      <c r="B475" t="inlineStr">
+      <c r="B468" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
     </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
+    <row r="469">
+      <c r="A469" t="inlineStr">
         <is>
           <t>00476_多选题
 荀子提倡的教师伦理包括以下哪些？（     ）
@@ -8503,14 +8384,14 @@
 D.忽视学生需求；</t>
         </is>
       </c>
-      <c r="B476" t="inlineStr">
+      <c r="B469" t="inlineStr">
         <is>
           <t>BC</t>
         </is>
       </c>
     </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
+    <row r="470">
+      <c r="A470" t="inlineStr">
         <is>
           <t>00477_多选题
 在教育资源分配中，教师应如何体现教育良心？（     ）
@@ -8520,14 +8401,14 @@
 D.优先分配给成绩优异的学生；</t>
         </is>
       </c>
-      <c r="B477" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
+    <row r="471">
+      <c r="A471" t="inlineStr">
         <is>
           <t>00478_多选题
 教师伦理学的实践原则——爱党爱国，要求教师（     ）。
@@ -8537,14 +8418,14 @@
 D.不仅要在言语上表达对祖国的热爱，更要在行动上践行爱国之情；</t>
         </is>
       </c>
-      <c r="B478" t="inlineStr">
+      <c r="B471" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
+    <row r="472">
+      <c r="A472" t="inlineStr">
         <is>
           <t>00479_多选题
 陶行知提倡的教育理念包括：（     ）。
@@ -8554,14 +8435,14 @@
 D.提倡教师要热爱学生；</t>
         </is>
       </c>
-      <c r="B479" t="inlineStr">
+      <c r="B472" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
+    <row r="473">
+      <c r="A473" t="inlineStr">
         <is>
           <t>00480_多选题
 加强自我修养是完善教师道德境界的良好途径。下列属于加强自我修养的是（     ）。
@@ -8571,14 +8452,14 @@
 D.君子慎其独也；</t>
         </is>
       </c>
-      <c r="B480" t="inlineStr">
+      <c r="B473" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
+    <row r="474">
+      <c r="A474" t="inlineStr">
         <is>
           <t>00481_多选题
 关于教师道德的调节功能，以下说法正确的是（     ）。
@@ -8588,14 +8469,14 @@
 D.道德调节最终依靠道德自觉性来实现；</t>
         </is>
       </c>
-      <c r="B481" t="inlineStr">
+      <c r="B474" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
+    <row r="475">
+      <c r="A475" t="inlineStr">
         <is>
           <t>00482_多选题
 高校教师社会服务对加强高校与社会的联系有何积极作用？（     ）
@@ -8605,14 +8486,14 @@
 D.促进了高校科研成果在社会中的有效转化与应用；</t>
         </is>
       </c>
-      <c r="B482" t="inlineStr">
+      <c r="B475" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
+    <row r="476">
+      <c r="A476" t="inlineStr">
         <is>
           <t>00483_多选题
 21世纪初至今，教师专业伦理研究的发展趋势包括：（     ）。
@@ -8622,14 +8503,14 @@
 D.教育过程中保障学生的权益；</t>
         </is>
       </c>
-      <c r="B483" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
+    <row r="477">
+      <c r="A477" t="inlineStr">
         <is>
           <t>00484_多选题
 关于教师道德系统诸要素之间的关系，以下说法正确的是（     ）。
@@ -8639,14 +8520,14 @@
 D.师德意识是师德关系的反应，是师德规范形成的思想前提；</t>
         </is>
       </c>
-      <c r="B484" t="inlineStr">
+      <c r="B477" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
+    <row r="478">
+      <c r="A478" t="inlineStr">
         <is>
           <t>00485_多选题
 与其他职业良心相比，教师道德良心的特征主要有（     ）。
@@ -8656,14 +8537,14 @@
 D.缺乏自觉性；</t>
         </is>
       </c>
-      <c r="B485" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
+    <row r="479">
+      <c r="A479" t="inlineStr">
         <is>
           <t>00486_多选题
 在科研指导中，教师应帮助学生提升哪些能力？（     ）
@@ -8673,14 +8554,14 @@
 D.创新能力；</t>
         </is>
       </c>
-      <c r="B486" t="inlineStr">
+      <c r="B479" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
+    <row r="480">
+      <c r="A480" t="inlineStr">
         <is>
           <t>00487_多选题
 教师在参与学术评审活动时应遵循的原则包括（     ）。
@@ -8690,14 +8571,14 @@
 D.优先考虑个人关系；</t>
         </is>
       </c>
-      <c r="B487" t="inlineStr">
+      <c r="B480" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
+    <row r="481">
+      <c r="A481" t="inlineStr">
         <is>
           <t>00488_多选题
 中世纪教育中，教师职业道德的特点包括：（     ）。
@@ -8707,14 +8588,14 @@
 D.强调教师个人的道德修养；</t>
         </is>
       </c>
-      <c r="B488" t="inlineStr">
+      <c r="B481" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
+    <row r="482">
+      <c r="A482" t="inlineStr">
         <is>
           <t>00489_多选题
 教师伦理学中“关爱学生”的实践原则，要求教师（     ）。
@@ -8724,14 +8605,14 @@
 D.以包容、平等的心态对待所有学生；</t>
         </is>
       </c>
-      <c r="B489" t="inlineStr">
+      <c r="B482" t="inlineStr">
         <is>
           <t>ACD</t>
         </is>
       </c>
     </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
+    <row r="483">
+      <c r="A483" t="inlineStr">
         <is>
           <t>00490_多选题
 为了保障科研伦理的实践，需要采取哪些措施？（     ）
@@ -8741,14 +8622,14 @@
 D.明确利益冲突管理；</t>
         </is>
       </c>
-      <c r="B490" t="inlineStr">
+      <c r="B483" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
+    <row r="484">
+      <c r="A484" t="inlineStr">
         <is>
           <t>00491_多选题
 高校教师在提升自身职业道德水平时应采取哪些措施？（     ）
@@ -8758,14 +8639,14 @@
 D.只关注学术成果的发表；</t>
         </is>
       </c>
-      <c r="B491" t="inlineStr">
+      <c r="B484" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
     </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
+    <row r="485">
+      <c r="A485" t="inlineStr">
         <is>
           <t>00492_多选题
 教师伦理学认为，教师在教育教学的过程中应当（     ）。
@@ -8775,14 +8656,14 @@
 D.避免任何形式的歧视与偏见，确保每个学生都能在公平、公正的环境中成长，实现自我价值；</t>
         </is>
       </c>
-      <c r="B492" t="inlineStr">
+      <c r="B485" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
+    <row r="486">
+      <c r="A486" t="inlineStr">
         <is>
           <t>00493_多选题
 高校教师在处理学生事务时，应避免哪些行为？（     ）
@@ -8792,14 +8673,14 @@
 D.忽视学生的心理需求；</t>
         </is>
       </c>
-      <c r="B493" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>ABD</t>
         </is>
       </c>
     </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
+    <row r="487">
+      <c r="A487" t="inlineStr">
         <is>
           <t>00494_多选题
 我国高校教师道德现状还存在着诸多问题，比较突出的有（     ）。
@@ -8809,14 +8690,14 @@
 D.敬业精神弱化；</t>
         </is>
       </c>
-      <c r="B494" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>ABCD</t>
         </is>
       </c>
     </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
+    <row r="488">
+      <c r="A488" t="inlineStr">
         <is>
           <t>00495_多选题
 在教学设计中，教师应如何体现教育良心？（     ）
@@ -8826,30 +8707,121 @@
 D.提供适当的学习支持；</t>
         </is>
       </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>ACD</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>00496_判断题
+教育良心只在教学中体现，与科研和学生管理无关。</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>00497_判断题
+伦理理想是对伦理理想人格的自觉追求。</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>00498_判断题
+21世纪之后，教师伦理的发展趋向以“道德”取代“伦理”。</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>00499_判断题
+高校教师作为知识的探索者和创新者，其学术行为直接影响着学术生态的健康与繁荣。</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>00500_判断题
+韩愈认为教师的主要任务是“传道、授业、解惑”，其中“授业”是教师的首要任务。</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>错</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>00501_判断题
+自由作为人类追求幸福与发展的重要基础，是人性尊严与创造力的源泉。</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>对</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>00502_判断题
+伦理行为是衡量教师职业伦理水平高低的主要标志。</t>
+        </is>
+      </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>ACD</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>00496_判断题
-教育良心只在教学中体现，与科研和学生管理无关。</t>
+          <t>00503_判断题
+教师职业行为的恶可以划分为不同的等级。</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>00497_判断题
-伦理理想是对伦理理想人格的自觉追求。</t>
+          <t>00504_判断题
+终身学习是教师职业的内在要求。</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -8861,8 +8833,8 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>00498_判断题
-21世纪之后，教师伦理的发展趋向以“道德”取代“伦理”。</t>
+          <t>00505_判断题
+判断教师行为是非善恶的最根本的道德标准是关爱学生。</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -8874,47 +8846,47 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>00499_判断题
-高校教师作为知识的探索者和创新者，其学术行为直接影响着学术生态的健康与繁荣。</t>
+          <t>00506_判断题
+诺丁斯提出的关怀伦理学没有强调教师与学生之间的情感联系。</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>00500_判断题
-韩愈认为教师的主要任务是“传道、授业、解惑”，其中“授业”是教师的首要任务。</t>
+          <t>00507_判断题
+高校应制定和完善相关政策与规章制度，以明确教师社会服务的职责与权益，并建立科学合理的考核和奖励机制。</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>00501_判断题
-自由作为人类追求幸福与发展的重要基础，是人性尊严与创造力的源泉。</t>
+          <t>00508_判断题
+制度伦理可以完全替代科研者的道德判断。</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>00502_判断题
-伦理行为是衡量教师职业伦理水平高低的主要标志。</t>
+          <t>00509_判断题
+师生关系伦理的核心在于三个基本维度，即平等、尊重与和谐，其中和谐则是这种关系追求的最终目标。</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -8926,8 +8898,8 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>00503_判断题
-教师职业行为的恶可以划分为不同的等级。</t>
+          <t>00510_判断题
+良好的师生关系伦理有助于增强教师的职业幸福感与成就感，并激励教师更加投入地工作，不断提升自己的专业素养和教育能力。</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -8939,8 +8911,8 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>00504_判断题
-终身学习是教师职业的内在要求。</t>
+          <t>00511_判断题
+科研过程中的透明度是确保研究结果可靠性的重要因素之一。</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -8952,8 +8924,8 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>00505_判断题
-判断教师行为是非善恶的最根本的道德标准是关爱学生。</t>
+          <t>00512_判断题
+所谓教师的非道德行为就是并非完全出自道德意志的行为。</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -8965,34 +8937,34 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>00506_判断题
-诺丁斯提出的关怀伦理学没有强调教师与学生之间的情感联系。</t>
+          <t>00513_判断题
+学术保障是高校教师社会服务伦理建构的重要支撑，因为它有助于推动科研成果的转化和应用。</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>00507_判断题
-高校应制定和完善相关政策与规章制度，以明确教师社会服务的职责与权益，并建立科学合理的考核和奖励机制。</t>
+          <t>00514_判断题
+苏格拉底认为教师应以权威自居，与学生进行不平等的对话。</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>00508_判断题
-制度伦理可以完全替代科研者的道德判断。</t>
+          <t>00515_判断题
+信息技术革命主要特征是基因工程、克隆技术和生物医药的突破。</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -9004,34 +8976,34 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>00509_判断题
-师生关系伦理的核心在于三个基本维度，即平等、尊重与和谐，其中和谐则是这种关系追求的最终目标。</t>
+          <t>00516_判断题
+教师伦理的评价功能是基于明确目的和统一标准，对教师的单一维度的评估，旨在促进教师的专业成长与道德提升。</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>00510_判断题
-良好的师生关系伦理有助于增强教师的职业幸福感与成就感，并激励教师更加投入地工作，不断提升自己的专业素养和教育能力。</t>
+          <t>00517_判断题
+高校教师在科研指导中可以根据学生的家庭背景对实验结果进行调整。</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>00511_判断题
-科研过程中的透明度是确保研究结果可靠性的重要因素之一。</t>
+          <t>00518_判断题
+《中小学教师职业道德规范》自1985年起颁布并多次修订，以提升教师素质。</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -9043,47 +9015,47 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>00512_判断题
-所谓教师的非道德行为就是并非完全出自道德意志的行为。</t>
+          <t>00519_判断题
+权利与利益要求我们在尊重个体权利的同时，也要考虑到社会整体利益与长远利益的重要性，通过理性的对话与协商，寻求各方都能接受的解决方案。</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>00513_判断题
-学术保障是高校教师社会服务伦理建构的重要支撑，因为它有助于推动科研成果的转化和应用。</t>
+          <t>00520_判断题
+爱岗敬业是教师职业道德的基本要求。</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>00514_判断题
-苏格拉底认为教师应以权威自居，与学生进行不平等的对话。</t>
+          <t>00521_判断题
+爱党爱国被是良好教师伦理建构的首要原则，是每位教育工作者不可动摇的信念。这一准则不仅象征着教师个体对国家和执政党的深切敬仰与忠诚，而且体现了教育事业所承载的重大社会责任与历史担当。</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>00515_判断题
-信息技术革命主要特征是基因工程、克隆技术和生物医药的突破。</t>
+          <t>00522_判断题
+掌握伦理概念是教师职业伦理认识的感性阶段，是伦理认识的概括化过程。</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -9095,47 +9067,47 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>00516_判断题
-教师伦理的评价功能是基于明确目的和统一标准，对教师的单一维度的评估，旨在促进教师的专业成长与道德提升。</t>
+          <t>00523_判断题
+教师道德行为的选择，可以反映教师不同道德水平和境界。</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>00517_判断题
-高校教师在科研指导中可以根据学生的家庭背景对实验结果进行调整。</t>
+          <t>00524_判断题
+应用伦理学在理论研究与实践应用之间建立了更加紧密的联系，成为推动社会进步和文明发展的重要力量。</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>00518_判断题
-《中小学教师职业道德规范》自1985年起颁布并多次修订，以提升教师素质。</t>
+          <t>00525_判断题
+高校教师社会服务的伦理特性之一是通过非学术性方式服务经济发展。</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>00519_判断题
-权利与利益要求我们在尊重个体权利的同时，也要考虑到社会整体利益与长远利益的重要性，通过理性的对话与协商，寻求各方都能接受的解决方案。</t>
+          <t>00526_判断题
+信念是教师伦理修养的核心。</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -9147,47 +9119,47 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>00520_判断题
-爱岗敬业是教师职业道德的基本要求。</t>
+          <t>00527_判断题
+柏拉图认为教师应出于对智慧的热爱和对教育的责任进行教学。</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>00521_判断题
-爱党爱国被是良好教师伦理建构的首要原则，是每位教育工作者不可动摇的信念。这一准则不仅象征着教师个体对国家和执政党的深切敬仰与忠诚，而且体现了教育事业所承载的重大社会责任与历史担当。</t>
+          <t>00528_判断题
+规范伦理学是研究伦理规范和价值观念的学科，其关注的是伦理学的本质和基础。</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>00522_判断题
-掌握伦理概念是教师职业伦理认识的感性阶段，是伦理认识的概括化过程。</t>
+          <t>00529_判断题
+教书育人是人民教师应尽的道德义务。</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>00523_判断题
-教师道德行为的选择，可以反映教师不同道德水平和境界。</t>
+          <t>00530_判断题
+虚假信息传播会侵蚀社会对学术的信任。</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -9199,8 +9171,8 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>00524_判断题
-应用伦理学在理论研究与实践应用之间建立了更加紧密的联系，成为推动社会进步和文明发展的重要力量。</t>
+          <t>00531_判断题
+道德信念是道德品质的核心。</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -9212,8 +9184,8 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>00525_判断题
-高校教师社会服务的伦理特性之一是通过非学术性方式服务经济发展。</t>
+          <t>00532_判断题
+教师的道德调节主要是自律性的自我调节。</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -9225,34 +9197,34 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>00526_判断题
-信念是教师伦理修养的核心。</t>
+          <t>00533_判断题
+教师伦理激励功能的具体体现就是工作绩效激励。</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>00527_判断题
-柏拉图认为教师应出于对智慧的热爱和对教育的责任进行教学。</t>
+          <t>00534_判断题
+20世纪60年代至90年代，教师专业化运动主要发生在日本。</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>00528_判断题
-规范伦理学是研究伦理规范和价值观念的学科，其关注的是伦理学的本质和基础。</t>
+          <t>00535_判断题
+他律和自律是教师道德修养过程中的两个不同阶段，自律是他律充分发挥作用的重要基础。</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -9264,8 +9236,8 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>00529_判断题
-教书育人是人民教师应尽的道德义务。</t>
+          <t>00536_判断题
+博耶将社会服务纳入应用的学术范畴，认为其是教学和研究的重要组成部分。</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -9277,8 +9249,8 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>00530_判断题
-虚假信息传播会侵蚀社会对学术的信任。</t>
+          <t>00537_判断题
+教师道德自律的最高实现形式是教师良心。</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -9290,8 +9262,8 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>00531_判断题
-道德信念是道德品质的核心。</t>
+          <t>00538_判断题
+教师在处理师生关系时，应尊重学生的合法权利，并公正处理学生事务。</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -9303,8 +9275,8 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>00532_判断题
-教师的道德调节主要是自律性的自我调节。</t>
+          <t>00539_判断题
+教师通过社会服务，只能提升教育质量，而无法推动学术研究。</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -9316,34 +9288,34 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>00533_判断题
-教师伦理激励功能的具体体现就是工作绩效激励。</t>
+          <t>00540_判断题
+学术研究伦理作为学术研究领域的基石，是每一位学者，特别是高校教师必须坚守的道德底线和行为准则。</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>00534_判断题
-20世纪60年代至90年代，教师专业化运动主要发生在日本。</t>
+          <t>00541_判断题
+促进文明进步的重要力量，要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>00535_判断题
-他律和自律是教师道德修养过程中的两个不同阶段，自律是他律充分发挥作用的重要基础。</t>
+          <t>00542_判断题
+教师道德修养是一个短期内就可以实现的过程。</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -9355,21 +9327,21 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>00536_判断题
-博耶将社会服务纳入应用的学术范畴，认为其是教学和研究的重要组成部分。</t>
+          <t>00543_判断题
+联合国教科文组织在1996年通过的《关于教师地位的建议书》没有指出教师道德的指导原则。</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>00537_判断题
-教师道德自律的最高实现形式是教师良心。</t>
+          <t>00544_判断题
+拓展师德建设的途径一方面可以将伦理素养纳入教师职业素质训练体系之中，另一方面可以使伦理评价贯穿于教育活动的全过程，成为评价教师工作和业绩的基本指标。</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -9381,34 +9353,34 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>00538_判断题
-教师在处理师生关系时，应尊重学生的合法权利，并公正处理学生事务。</t>
+          <t>00545_判断题
+伦理行为是教师所表现出来的有利于他人及社会的行为。</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>00539_判断题
-教师通过社会服务，只能提升教育质量，而无法推动学术研究。</t>
+          <t>00546_判断题
+高校教师伦理的结构是一个以德性伦理为核心、以规范伦理为具体内容的综合体系。</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>00540_判断题
-学术研究伦理作为学术研究领域的基石，是每一位学者，特别是高校教师必须坚守的道德底线和行为准则。</t>
+          <t>00547_判断题
+在应用伦理学的视野中，自由与限制的平衡，需要我们在尊重个体权利的同时，也考虑到社会责任与道德约束的重要性。这要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -9420,34 +9392,34 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>00541_判断题
-促进文明进步的重要力量，要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
+          <t>00548_判断题
+制定社会主义教师道德原则仅仅需要依据一般社会道德原则的要求。</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>00542_判断题
-教师道德修养是一个短期内就可以实现的过程。</t>
+          <t>00549_判断题
+人们应当具备道德自觉性和道德责任感，能够在面对诱惑与挑战时坚守道德底线。</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>00543_判断题
-联合国教科文组织在1996年通过的《关于教师地位的建议书》没有指出教师道德的指导原则。</t>
+          <t>00550_判断题
+教师在处理学生心理问题时，应当忽视学生的情感和心理健康，专注于学术表现。</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -9459,8 +9431,8 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>00544_判断题
-拓展师德建设的途径一方面可以将伦理素养纳入教师职业素质训练体系之中，另一方面可以使伦理评价贯穿于教育活动的全过程，成为评价教师工作和业绩的基本指标。</t>
+          <t>00551_判断题
+师德评价是通过收集学生、同事、家长及社会的多方反馈，对师德表现进行细致入微的全面审视。</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -9472,21 +9444,21 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>00545_判断题
-伦理行为是教师所表现出来的有利于他人及社会的行为。</t>
+          <t>00552_判断题
+尊重学生作为教师伦理学的首要原则，强调教师应以平等、包容的心态对待每一位学生，充分认识到每个学生都是独一无二的个体，拥有各自独特的个性、兴趣与潜能。</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>00546_判断题
-高校教师伦理的结构是一个以德性伦理为核心、以规范伦理为具体内容的综合体系。</t>
+          <t>00553_判断题
+教育良心的形成需要教师通过学习、反思和实践，不断提升自己的职业道德水平。</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -9498,8 +9470,8 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>00547_判断题
-在应用伦理学的视野中，自由与限制的平衡，需要我们在尊重个体权利的同时，也考虑到社会责任与道德约束的重要性。这要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
+          <t>00554_判断题
+只有在现实的与他人相处的道德关系中，才能改造自己的品质。</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -9511,34 +9483,34 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>00548_判断题
-制定社会主义教师道德原则仅仅需要依据一般社会道德原则的要求。</t>
+          <t>00555_判断题
+在伦理学的视野中，善与恶并非简单的二元对立，而是涉及复杂的价值判断与道德选择。</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>00549_判断题
-人们应当具备道德自觉性和道德责任感，能够在面对诱惑与挑战时坚守道德底线。</t>
+          <t>00556_判断题
+很多教师从一定程度上将自己的工作比作“良心活”，说明教师职业道德具有深远性。</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>00550_判断题
-教师在处理学生心理问题时，应当忽视学生的情感和心理健康，专注于学术表现。</t>
+          <t>00557_判断题
+师德的灵魂是加强反思。</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -9550,8 +9522,8 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>00551_判断题
-师德评价是通过收集学生、同事、家长及社会的多方反馈，对师德表现进行细致入微的全面审视。</t>
+          <t>00558_判断题
+荀子认为教师应该与“天、地、君、亲”并立，并且对教师有严格的要求。</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -9563,21 +9535,21 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>00552_判断题
-尊重学生作为教师伦理学的首要原则，强调教师应以平等、包容的心态对待每一位学生，充分认识到每个学生都是独一无二的个体，拥有各自独特的个性、兴趣与潜能。</t>
+          <t>00559_判断题
+排除障碍的能力和毅力不是评价一个人是否具有一定的伦理品质的重要内容。</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>00553_判断题
-教育良心的形成需要教师通过学习、反思和实践，不断提升自己的职业道德水平。</t>
+          <t>00560_判断题
+20世纪90年代至21世纪初期，教师伦理研究的焦点集中在教育实践中的具体伦理议题上。</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -9589,8 +9561,8 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>00554_判断题
-只有在现实的与他人相处的道德关系中，才能改造自己的品质。</t>
+          <t>00561_判断题
+教师伦理修养是一个由认识、情感、意志、信念、行为这些构成伦理规范的各个方面或各种因素相互作用的综合过程。</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -9602,8 +9574,8 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>00555_判断题
-在伦理学的视野中，善与恶并非简单的二元对立，而是涉及复杂的价值判断与道德选择。</t>
+          <t>00562_判断题
+包容的心态对待每一位学生，教师不仅要关注学生的学习情况与学业成就，还要关心他们的身心健康与情感需求。</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -9615,34 +9587,34 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>00556_判断题
-很多教师从一定程度上将自己的工作比作“良心活”，说明教师职业道德具有深远性。</t>
+          <t>00563_判断题
+法律不仅维护了教育行业的良好秩序，也彰显了国家对于教育事业的高度重视与严格监管。</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>00557_判断题
-师德的灵魂是加强反思。</t>
+          <t>00564_判断题
+教书育人是教师的天职和道德核心。</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>00558_判断题
-荀子认为教师应该与“天、地、君、亲”并立，并且对教师有严格的要求。</t>
+          <t>00565_判断题
+教师的公正伦理要求他们在处理学生事务时保持中立，并遵循既定规则。</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -9654,34 +9626,34 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>00559_判断题
-排除障碍的能力和毅力不是评价一个人是否具有一定的伦理品质的重要内容。</t>
+          <t>00566_判断题
+技术中性论认为技术应用的后果与技术本身无关。</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>00560_判断题
-20世纪90年代至21世纪初期，教师伦理研究的焦点集中在教育实践中的具体伦理议题上。</t>
+          <t>00567_判断题
+教师在科研活动中，可以为了快速发表成果而适当夸大实验结果。</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>00561_判断题
-教师伦理修养是一个由认识、情感、意志、信念、行为这些构成伦理规范的各个方面或各种因素相互作用的综合过程。</t>
+          <t>00568_判断题
+教师公正最基本也是最核心的内容是公平合理的评价和对待每个学生。</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -9693,8 +9665,8 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>00562_判断题
-包容的心态对待每一位学生，教师不仅要关注学生的学习情况与学业成就，还要关心他们的身心健康与情感需求。</t>
+          <t>00569_判断题
+权利与利益是伦理冲突的焦点，它关乎个体或群体在追求自身利益时如何平衡与他人的权利关系，以及如何在多元利益诉求中寻找共识与妥协。</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -9706,21 +9678,21 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>00563_判断题
-法律不仅维护了教育行业的良好秩序，也彰显了国家对于教育事业的高度重视与严格监管。</t>
+          <t>00570_判断题
+高校教师社会服务必须完全无偿，不能有任何形式的报酬。</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>00564_判断题
-教书育人是教师的天职和道德核心。</t>
+          <t>00571_判断题
+诚实与信任作为应用伦理学中的基础道德要求，是构建良好道德关系与促进社会合作的重要基石。</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -9732,8 +9704,8 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>00565_判断题
-教师的公正伦理要求他们在处理学生事务时保持中立，并遵循既定规则。</t>
+          <t>00572_判断题
+教育部发布的指导意见强调对学术不端行为要突出“严”的主基调，从严从重处理。</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -9745,8 +9717,8 @@
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>00566_判断题
-技术中性论认为技术应用的后果与技术本身无关。</t>
+          <t>00573_判断题
+工作绩效激励通过表彰和奖励在师德方面表现突出的教师，不仅增强了他们的荣誉感和归属感，更在全社会范围内营造了尊师重教的良好氛围。</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -9758,21 +9730,21 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>00567_判断题
-教师在科研活动中，可以为了快速发表成果而适当夸大实验结果。</t>
+          <t>00574_判断题
+孔子的思想中对教师提出了“学而不厌”和“诲人不倦”等要求。</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>00568_判断题
-教师公正最基本也是最核心的内容是公平合理的评价和对待每个学生。</t>
+          <t>00575_判断题
+教师伦理修养以将他律的教师伦理原则及其规范转变为教师个体内在的伦理品质为目标。</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -9784,8 +9756,8 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>00569_判断题
-权利与利益是伦理冲突的焦点，它关乎个体或群体在追求自身利益时如何平衡与他人的权利关系，以及如何在多元利益诉求中寻找共识与妥协。</t>
+          <t>00576_判断题
+教师职业伦理情感是教育实践的产物。</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -9797,8 +9769,8 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>00570_判断题
-高校教师社会服务必须完全无偿，不能有任何形式的报酬。</t>
+          <t>00577_判断题
+师德修养以教师培训进修为主要途径。</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
@@ -9810,8 +9782,8 @@
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>00571_判断题
-诚实与信任作为应用伦理学中的基础道德要求，是构建良好道德关系与促进社会合作的重要基石。</t>
+          <t>00578_判断题
+朱熹强调教师要“知行合一”，即认知和行动要相结合。</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -9823,8 +9795,8 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>00572_判断题
-教育部发布的指导意见强调对学术不端行为要突出“严”的主基调，从严从重处理。</t>
+          <t>00579_判断题
+衡量和判断教师行为善恶的最高道德标准是教师职业道德基本原则。</t>
         </is>
       </c>
       <c r="B572" t="inlineStr">
@@ -9836,47 +9808,47 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>00573_判断题
-工作绩效激励通过表彰和奖励在师德方面表现突出的教师，不仅增强了他们的荣誉感和归属感，更在全社会范围内营造了尊师重教的良好氛围。</t>
+          <t>00580_判断题
+公正处理意味着教师在处理学生事务时，应根据个人情感和社会压力做出决策。</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>00574_判断题
-孔子的思想中对教师提出了“学而不厌”和“诲人不倦”等要求。</t>
+          <t>00581_判断题
+教师在学习职业伦理规范时，首先应有一定的间接伦理经验。</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>00575_判断题
-教师伦理修养以将他律的教师伦理原则及其规范转变为教师个体内在的伦理品质为目标。</t>
+          <t>00582_判断题
+教师在处理学生间的冲突时，可以根据学生的学术成绩决定处理方式。</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>00576_判断题
-教师职业伦理情感是教育实践的产物。</t>
+          <t>00583_判断题
+“慎独”是教师在职业伦理修养中一种十分有效且重要的修养途径。</t>
         </is>
       </c>
       <c r="B576" t="inlineStr">
@@ -9888,8 +9860,8 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>00577_判断题
-师德修养以教师培训进修为主要途径。</t>
+          <t>00584_判断题
+教师道德良心的表现形式是绝对客观的，但内部却是绝对主观的。</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -9901,8 +9873,8 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>00578_判断题
-朱熹强调教师要“知行合一”，即认知和行动要相结合。</t>
+          <t>00585_判断题
+抖音等平台通过个性化推荐算法加剧了信息茧房问题。</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -9914,8 +9886,8 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>00579_判断题
-衡量和判断教师行为善恶的最高道德标准是教师职业道德基本原则。</t>
+          <t>00586_判断题
+教师通过自我约束、自我监督、自我反思，更好地培养了教师职业道德情感、意志和信念。这属于努力做到“慎独”的职业道德修养方法。</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -9927,8 +9899,8 @@
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>00580_判断题
-公正处理意味着教师在处理学生事务时，应根据个人情感和社会压力做出决策。</t>
+          <t>00587_判断题
+高校教师在社会服务中必须完全避免任何与经济利益相关的活动，以保持学术的纯粹性。</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -9940,34 +9912,34 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>00581_判断题
-教师在学习职业伦理规范时，首先应有一定的间接伦理经验。</t>
+          <t>00588_判断题
+教师职业道德评价的社会行为评价标准是衡量、判断教师教育行为善恶的道德行为的尺度和准绳。</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>00582_判断题
-教师在处理学生间的冲突时，可以根据学生的学术成绩决定处理方式。</t>
+          <t>00589_判断题
+高校教师应以服务社会为己任，利用自身的专业特长和学术资源，参与解决社会中存在的实际问题。</t>
         </is>
       </c>
       <c r="B582" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>00583_判断题
-“慎独”是教师在职业伦理修养中一种十分有效且重要的修养途径。</t>
+          <t>00590_判断题
+教师伦理学认为，教师应当积极参加科研学术活动。</t>
         </is>
       </c>
       <c r="B583" t="inlineStr">
@@ -9979,8 +9951,8 @@
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>00584_判断题
-教师道德良心的表现形式是绝对客观的，但内部却是绝对主观的。</t>
+          <t>00591_判断题
+高校教师在社会服务中若采用非学术性方式回应社会需求，是符合其社会服务本质的。</t>
         </is>
       </c>
       <c r="B584" t="inlineStr">
@@ -9992,8 +9964,8 @@
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>00585_判断题
-抖音等平台通过个性化推荐算法加剧了信息茧房问题。</t>
+          <t>00592_判断题
+徐特立认为优秀教师应将“经师”和“人师”两种角色结合起来。</t>
         </is>
       </c>
       <c r="B585" t="inlineStr">
@@ -10005,47 +9977,47 @@
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>00586_判断题
-教师通过自我约束、自我监督、自我反思，更好地培养了教师职业道德情感、意志和信念。这属于努力做到“慎独”的职业道德修养方法。</t>
+          <t>00593_判断题
+教师在科研过程中可以忽略数据的真实性，以追求更好的研究成果。</t>
         </is>
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>00587_判断题
-高校教师在社会服务中必须完全避免任何与经济利益相关的活动，以保持学术的纯粹性。</t>
+          <t>00594_判断题
+教育良心促使教师在教学设计中关注学生的个体差异和全面发展。</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>00588_判断题
-教师职业道德评价的社会行为评价标准是衡量、判断教师教育行为善恶的道德行为的尺度和准绳。</t>
+          <t>00595_判断题
+技术建构论强调技术创新是线性过程，不受外界影响。</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>00589_判断题
-高校教师应以服务社会为己任，利用自身的专业特长和学术资源，参与解决社会中存在的实际问题。</t>
+          <t>00596_判断题
+教师伦理情感的培养具有评价、调节、信号方面的积极作用。</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
@@ -10057,8 +10029,8 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>00590_判断题
-教师伦理学认为，教师应当积极参加科研学术活动。</t>
+          <t>00597_判断题
+师德原则和规范的有效性和权威性对教师行为的约束力量由道德评价来显示和实现。</t>
         </is>
       </c>
       <c r="B590" t="inlineStr">
@@ -10070,8 +10042,8 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>00591_判断题
-高校教师在社会服务中若采用非学术性方式回应社会需求，是符合其社会服务本质的。</t>
+          <t>00598_判断题
+“苟正其身矣，于从政乎何有？不能正其身，如正人何？”这句话体现了教师道德基本原则中的教育人道主义原则。</t>
         </is>
       </c>
       <c r="B591" t="inlineStr">
@@ -10083,21 +10055,21 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>00592_判断题
-徐特立认为优秀教师应将“经师”和“人师”两种角色结合起来。</t>
+          <t>00599_判断题
+道德目的是指人们表达道德行为的方式和方法。</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>00593_判断题
-教师在科研过程中可以忽略数据的真实性，以追求更好的研究成果。</t>
+          <t>00600_判断题
+高校教师社会服务伦理的建构，仅需要教师的自觉性和学术能力，无需外部保障。</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
@@ -10109,73 +10081,73 @@
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>00594_判断题
-教育良心促使教师在教学设计中关注学生的个体差异和全面发展。</t>
+          <t>00601_判断题
+教师在制定课程评价标准时，可以根据学生的个人背景进行调整。</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>00595_判断题
-技术建构论强调技术创新是线性过程，不受外界影响。</t>
+          <t>00602_判断题
+学术研究伦理要求高校教师不仅要在学术领域追求卓越，更要将个人的专业知识和技能转化为服务社会的实际行动。</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>00596_判断题
-教师伦理情感的培养具有评价、调节、信号方面的积极作用。</t>
+          <t>00603_判断题
+教师道德他律中的实在性特点是指教师在认知心理上已经扬弃了道德的实在性倾向，代之以“问心无愧”的道德心理倾向。</t>
         </is>
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>00597_判断题
-师德原则和规范的有效性和权威性对教师行为的约束力量由道德评价来显示和实现。</t>
+          <t>00604_判断题
+教育良心仅要求教师在教学过程中关注学生的学术成绩。</t>
         </is>
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>00598_判断题
-“苟正其身矣，于从政乎何有？不能正其身，如正人何？”这句话体现了教师道德基本原则中的教育人道主义原则。</t>
+          <t>00605_判断题
+教师伦理修养，是指教师为形成良好的伦理品质所进行的自我诊断、自我教育、自我改造、自我陶冶、自我锤炼的过程，以及所要达到的水平。</t>
         </is>
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>00599_判断题
-道德目的是指人们表达道德行为的方式和方法。</t>
+          <t>00606_判断题
+技术控制论主要关注技术如何提升生产效率和经济利益。</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
@@ -10187,34 +10159,34 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>00600_判断题
-高校教师社会服务伦理的建构，仅需要教师的自觉性和学术能力，无需外部保障。</t>
+          <t>00607_判断题
+专业敬业要求教师不仅要具备扎实的专业知识与技能，还要热爱教育事业，勤勉尽责，不断提升自己的教育教学水平，这要求教师在日常教学中注意观察学生的情绪变化与行为表现，及时发现并解决学生可能面临的问题与困扰。</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>00601_判断题
-教师在制定课程评价标准时，可以根据学生的个人背景进行调整。</t>
+          <t>00608_判断题
+教师道德评价在教师道德认识和教师职业道德行为的转化中，起着媒介作用。</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>00602_判断题
-学术研究伦理要求高校教师不仅要在学术领域追求卓越，更要将个人的专业知识和技能转化为服务社会的实际行动。</t>
+          <t>00609_判断题
+教育实践的长期性、复杂性决定了教师伦理修养必然也是一个复杂而长期的过程。</t>
         </is>
       </c>
       <c r="B602" t="inlineStr">
@@ -10226,8 +10198,8 @@
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>00603_判断题
-教师道德他律中的实在性特点是指教师在认知心理上已经扬弃了道德的实在性倾向，代之以“问心无愧”的道德心理倾向。</t>
+          <t>00610_判断题
+中国古代和近代对“教师专业伦理”和“教师职业道德”进行了明确区分。</t>
         </is>
       </c>
       <c r="B603" t="inlineStr">
@@ -10239,8 +10211,8 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>00604_判断题
-教育良心仅要求教师在教学过程中关注学生的学术成绩。</t>
+          <t>00611_判断题
+教师道德规范是一种非强制力的软约束规范，依靠教育和自律就可以促进教师道德水平的提升。</t>
         </is>
       </c>
       <c r="B604" t="inlineStr">
@@ -10252,8 +10224,8 @@
     <row r="605">
       <c r="A605" t="inlineStr">
         <is>
-          <t>00605_判断题
-教师伦理修养，是指教师为形成良好的伦理品质所进行的自我诊断、自我教育、自我改造、自我陶冶、自我锤炼的过程，以及所要达到的水平。</t>
+          <t>00612_判断题
+教师伦理修养需要遵循强化教师伦理认识、培养教师伦理情感、锤炼教师伦理意志、坚定教师伦理信念、践行教师伦理行为五个基本环节。</t>
         </is>
       </c>
       <c r="B605" t="inlineStr">
@@ -10265,21 +10237,21 @@
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>00606_判断题
-技术控制论主要关注技术如何提升生产效率和经济利益。</t>
+          <t>00613_判断题
+本质上而言，教师伦理修养是一个自觉认识和行为选择的过程。</t>
         </is>
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>00607_判断题
-专业敬业要求教师不仅要具备扎实的专业知识与技能，还要热爱教育事业，勤勉尽责，不断提升自己的教育教学水平，这要求教师在日常教学中注意观察学生的情绪变化与行为表现，及时发现并解决学生可能面临的问题与困扰。</t>
+          <t>00614_判断题
+教师只有通过坚守学术伦理，才能培养学生成为具有高尚品德和扎实学识的优秀人才。</t>
         </is>
       </c>
       <c r="B607" t="inlineStr">
@@ -10291,21 +10263,21 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>00608_判断题
-教师道德评价在教师道德认识和教师职业道德行为的转化中，起着媒介作用。</t>
+          <t>00615_判断题
+教师道德行为是纯粹道德意义上的行为。</t>
         </is>
       </c>
       <c r="B608" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>00609_判断题
-教育实践的长期性、复杂性决定了教师伦理修养必然也是一个复杂而长期的过程。</t>
+          <t>00616_判断题
+伦理义务要求高校教师遵守教学责任，准确传授知识，并公平对待每位学生。</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -10317,21 +10289,21 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t>00610_判断题
-中国古代和近代对“教师专业伦理”和“教师职业道德”进行了明确区分。</t>
+          <t>00617_判断题
+自省是人们由他律向自律转化的标志，它表明个体道德观念和行动的发展进入了自觉阶段。</t>
         </is>
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>00611_判断题
-教师道德规范是一种非强制力的软约束规范，依靠教育和自律就可以促进教师道德水平的提升。</t>
+          <t>00618_判断题
+科研从业者无需关注道德问题，只需追求技术突破。</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
@@ -10343,8 +10315,8 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>00612_判断题
-教师伦理修养需要遵循强化教师伦理认识、培养教师伦理情感、锤炼教师伦理意志、坚定教师伦理信念、践行教师伦理行为五个基本环节。</t>
+          <t>00619_判断题
+良好的师生关系伦理有助于构建积极向上的校园文化。</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
@@ -10356,8 +10328,8 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>00613_判断题
-本质上而言，教师伦理修养是一个自觉认识和行为选择的过程。</t>
+          <t>00620_判断题
+墨子的教育目的是“兼相爱、交相利”，并且主张教师要对学生进行积极教育。</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
@@ -10369,8 +10341,8 @@
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>00614_判断题
-教师只有通过坚守学术伦理，才能培养学生成为具有高尚品德和扎实学识的优秀人才。</t>
+          <t>00621_判断题
+科研伦理审查是确保科研活动符合伦理规范的重要环节。</t>
         </is>
       </c>
       <c r="B614" t="inlineStr">
@@ -10382,21 +10354,21 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>00615_判断题
-教师道德行为是纯粹道德意义上的行为。</t>
+          <t>00622_判断题
+社会监督不仅促进了教师个人职业道德的自觉提升，也形成广泛的道德共识，营造了全社会共同关注和支持教育事业的良好氛围。</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>00616_判断题
-伦理义务要求高校教师遵守教学责任，准确传授知识，并公平对待每位学生。</t>
+          <t>00623_判断题
+利益的评估与权衡等多个方面，要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
@@ -10408,8 +10380,8 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>00617_判断题
-自省是人们由他律向自律转化的标志，它表明个体道德观念和行动的发展进入了自觉阶段。</t>
+          <t>00624_判断题
+教师的道德行为首先是其对个人利益与社会教育事业整体利益的认识为选择根据。</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
@@ -10421,8 +10393,8 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>00618_判断题
-科研从业者无需关注道德问题，只需追求技术突破。</t>
+          <t>00625_判断题
+在个体层面，伦理学关注人们如何在日常生活中做出符合道德标准的选择。通过制定和实施道德法规、加强道德教育等措施，致力于营造一个充满正能量、积极向上的社会环境。</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
@@ -10434,8 +10406,8 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>00619_判断题
-良好的师生关系伦理有助于构建积极向上的校园文化。</t>
+          <t>00626_判断题
+教师职业道德的主要范畴是教师义务、教师良心、教师公正、教师荣誉、教师幸福等。</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -10447,21 +10419,21 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>00620_判断题
-墨子的教育目的是“兼相爱、交相利”，并且主张教师要对学生进行积极教育。</t>
+          <t>00627_判断题
+教育公正就是教育正义。</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>00621_判断题
-科研伦理审查是确保科研活动符合伦理规范的重要环节。</t>
+          <t>00628_判断题
+董仲舒提出“罢黜百家、独尊儒术”的主张，影响了中国封建社会的教师职业道德发展。</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -10473,8 +10445,8 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>00622_判断题
-社会监督不仅促进了教师个人职业道德的自觉提升，也形成广泛的道德共识，营造了全社会共同关注和支持教育事业的良好氛围。</t>
+          <t>00629_判断题
+将伦理标准融入工作绩效评估，不仅要关注教学任务，如学生成绩的提升、教学目标的实现等，还要深入探究教师在工作过程中的态度、方法与创新性。</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -10486,21 +10458,21 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>00623_判断题
-利益的评估与权衡等多个方面，要求我们不断探索如何在保障个体自由的同时，设定合理的界限与规范，以维护社会的和谐与稳定。</t>
+          <t>00630_判断题
+每个学生都是独一无二的个体，拥有不同的学习风格、兴趣爱好和成长需求。高校老师具备教育教学伦理，意味着能够尊重学生发展的不平衡性。</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>00624_判断题
-教师的道德行为首先是其对个人利益与社会教育事业整体利益的认识为选择根据。</t>
+          <t>00631_判断题
+教师的公正伦理要求他们在教学过程中公平对待每位学生，不因性别或背景而有偏袒。</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -10512,21 +10484,21 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>00625_判断题
-在个体层面，伦理学关注人们如何在日常生活中做出符合道德标准的选择。通过制定和实施道德法规、加强道德教育等措施，致力于营造一个充满正能量、积极向上的社会环境。</t>
+          <t>00632_判断题
+公正无私原则意味着在评价学生、分配教学资源时，教师应不受个人喜好、偏见或外部压力的影响，坚持客观、公正的标准</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>00626_判断题
-教师职业道德的主要范畴是教师义务、教师良心、教师公正、教师荣誉、教师幸福等。</t>
+          <t>00633_判断题
+反思性是伦理思维的本质。</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -10538,21 +10510,21 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>00627_判断题
-教育公正就是教育正义。</t>
+          <t>00634_判断题
+提高教师伦理素养需要提高处理师生关系、生生关系、同事关系、上下级关系的能力。</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>00628_判断题
-董仲舒提出“罢黜百家、独尊儒术”的主张，影响了中国封建社会的教师职业道德发展。</t>
+          <t>00635_判断题
+责任与义务是道德担当的基石，它关乎个体或群体在追求自身利益时如何平衡与他人的权利关系，以及如何在多元利益诉求中寻找共识与妥协。</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -10564,8 +10536,8 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>00629_判断题
-将伦理标准融入工作绩效评估，不仅要关注教学任务，如学生成绩的提升、教学目标的实现等，还要深入探究教师在工作过程中的态度、方法与创新性。</t>
+          <t>00636_判断题
+高校教师的伦理义务包括维护学术诚信，尊重他人的研究成果。</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -10577,21 +10549,21 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>00630_判断题
-每个学生都是独一无二的个体，拥有不同的学习风格、兴趣爱好和成长需求。高校老师具备教育教学伦理，意味着能够尊重学生发展的不平衡性。</t>
+          <t>00637_判断题
+社会主义道德区别于一切旧道德的根本标志是集体主义原则。</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>00631_判断题
-教师的公正伦理要求他们在教学过程中公平对待每位学生，不因性别或背景而有偏袒。</t>
+          <t>00638_判断题
+在应用伦理学的语境下，责任与义务不仅是道德行为的直接体现，更是构建社会秩序、维护公共利益的重要基石。它要求我们在面对决策与行动时，不仅要考虑自身的利益与欲望，更要审视其行为对他人、社会乃至未来世代的潜在影响。</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -10603,21 +10575,21 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>00632_判断题
-公正无私原则意味着在评价学生、分配教学资源时，教师应不受个人喜好、偏见或外部压力的影响，坚持客观、公正的标准</t>
+          <t>00639_判断题
+教学评价构成了评价功能的核心内容。</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>00633_判断题
-反思性是伦理思维的本质。</t>
+          <t>00640_判断题
+梁启超认为开民智是振兴中华的第一要务，因此师范教育非常重要。</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -10629,8 +10601,8 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>00634_判断题
-提高教师伦理素养需要提高处理师生关系、生生关系、同事关系、上下级关系的能力。</t>
+          <t>00641_判断题
+元伦理学是研究伦理学的基本概念和方法的学科。它关注的是伦理学的本质和基础。</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -10642,8 +10614,8 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>00635_判断题
-责任与义务是道德担当的基石，它关乎个体或群体在追求自身利益时如何平衡与他人的权利关系，以及如何在多元利益诉求中寻找共识与妥协。</t>
+          <t>00642_判断题
+高校教师在社会服务中不仅是知识的传播者，更是知识的生产者。</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -10655,73 +10627,73 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>00636_判断题
-高校教师的伦理义务包括维护学术诚信，尊重他人的研究成果。</t>
+          <t>00643_判断题
+高校教师在分配资源时，应优先考虑学生的学术表现，而不是公平性。</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>00637_判断题
-社会主义道德区别于一切旧道德的根本标志是集体主义原则。</t>
+          <t>00644_判断题
+教学业绩是教师伦理调节功能的核心。</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>00638_判断题
-在应用伦理学的语境下，责任与义务不仅是道德行为的直接体现，更是构建社会秩序、维护公共利益的重要基石。它要求我们在面对决策与行动时，不仅要考虑自身的利益与欲望，更要审视其行为对他人、社会乃至未来世代的潜在影响。</t>
+          <t>00645_判断题
+教师伦理的功能主要包括调节功能、评价功能、引导功能、约束功能。</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>00639_判断题
-教学评价构成了评价功能的核心内容。</t>
+          <t>00646_判断题
+在教师的伦理义务中，遵纪守法是指教师应遵守国家法律法规和学校规章制度。</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>00640_判断题
-梁启超认为开民智是振兴中华的第一要务，因此师范教育非常重要。</t>
+          <t>00647_判断题
+在教育资源分配中，教师应尽量避免将资源公开分配，以防止学生之间的竞争。</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>00641_判断题
-元伦理学是研究伦理学的基本概念和方法的学科。它关注的是伦理学的本质和基础。</t>
+          <t>00648_判断题
+行为指导为教师提供了清晰的行为准则和道德标尺，使教师能够做出符合教育规律和职业道德的决策。这些准则不仅融合了社会普遍认同的道德观念，还针对教育行业的特殊性。</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -10733,8 +10705,8 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>00642_判断题
-高校教师在社会服务中不仅是知识的传播者，更是知识的生产者。</t>
+          <t>00649_判断题
+教师在日常教学中应避免因个人偏好或外部压力影响对学生的评价。</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -10746,47 +10718,47 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>00643_判断题
-高校教师在分配资源时，应优先考虑学生的学术表现，而不是公平性。</t>
+          <t>00650_判断题
+“春蚕到死丝方尽，蜡炬成灰泪始干”这句话表明教师在教育教学的过程中应该遵守乐教勤业的教师道德基本原则。</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>00644_判断题
-教学业绩是教师伦理调节功能的核心。</t>
+          <t>00651_判断题
+限制是防止自由滥用、保障社会秩序与公共利益所必需的。</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>00645_判断题
-教师伦理的功能主要包括调节功能、评价功能、引导功能、约束功能。</t>
+          <t>00652_判断题
+公正与平等作为应用伦理学的核心价值追求，如同社会正义的灯塔，照亮了我们前行的道路。它不仅仅是对分配结果的考量，更是对分配过程、分配原则乃至社会结构的深刻反思，其涉及道德责任的界定、分配、执行与监督等多个层面。</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>00646_判断题
-在教师的伦理义务中，遵纪守法是指教师应遵守国家法律法规和学校规章制度。</t>
+          <t>00653_判断题
+教育良心要求高校教师在科研中保持数据的真实性和研究的科学性。</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -10798,21 +10770,21 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>00647_判断题
-在教育资源分配中，教师应尽量避免将资源公开分配，以防止学生之间的竞争。</t>
+          <t>00654_判断题
+教师道德规范的建立，必须同当今时代的进程和特征、同整个社会的经济、文化发展水平相适应，把道德的理想与现实性统一起来。</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
         <is>
-          <t>错</t>
+          <t>对</t>
         </is>
       </c>
     </row>
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>00648_判断题
-行为指导为教师提供了清晰的行为准则和道德标尺，使教师能够做出符合教育规律和职业道德的决策。这些准则不仅融合了社会普遍认同的道德观念，还针对教育行业的特殊性。</t>
+          <t>00655_判断题
+确立道德行为的标准，最终目的是指引道德实践的途径。</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -10824,115 +10796,24 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>00649_判断题
-教师在日常教学中应避免因个人偏好或外部压力影响对学生的评价。</t>
+          <t>00656_判断题
+教师职业道德行为的选择只是教师个人自由意志驱动的结果。</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>对</t>
+          <t>错</t>
         </is>
       </c>
     </row>
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>00650_判断题
-“春蚕到死丝方尽，蜡炬成灰泪始干”这句话表明教师在教育教学的过程中应该遵守乐教勤业的教师道德基本原则。</t>
-        </is>
-      </c>
-      <c r="B650" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>00651_判断题
-限制是防止自由滥用、保障社会秩序与公共利益所必需的。</t>
-        </is>
-      </c>
-      <c r="B651" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>00652_判断题
-公正与平等作为应用伦理学的核心价值追求，如同社会正义的灯塔，照亮了我们前行的道路。它不仅仅是对分配结果的考量，更是对分配过程、分配原则乃至社会结构的深刻反思，其涉及道德责任的界定、分配、执行与监督等多个层面。</t>
-        </is>
-      </c>
-      <c r="B652" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>00653_判断题
-教育良心要求高校教师在科研中保持数据的真实性和研究的科学性。</t>
-        </is>
-      </c>
-      <c r="B653" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr">
-        <is>
-          <t>00654_判断题
-教师道德规范的建立，必须同当今时代的进程和特征、同整个社会的经济、文化发展水平相适应，把道德的理想与现实性统一起来。</t>
-        </is>
-      </c>
-      <c r="B654" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr">
-        <is>
-          <t>00655_判断题
-确立道德行为的标准，最终目的是指引道德实践的途径。</t>
-        </is>
-      </c>
-      <c r="B655" t="inlineStr">
-        <is>
-          <t>对</t>
-        </is>
-      </c>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr">
-        <is>
-          <t>00656_判断题
-教师职业道德行为的选择只是教师个人自由意志驱动的结果。</t>
-        </is>
-      </c>
-      <c r="B656" t="inlineStr">
-        <is>
-          <t>错</t>
-        </is>
-      </c>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr">
-        <is>
           <t>00657_判断题
 教师伦理情感是教师产生高尚职业追求的动力源泉。</t>
         </is>
       </c>
-      <c r="B657" t="inlineStr">
+      <c r="B650" t="inlineStr">
         <is>
           <t>对</t>
         </is>
